--- a/Excel/02_BD_Venta_IZIED.xlsx
+++ b/Excel/02_BD_Venta_IZIED.xlsx
@@ -8,15 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Relatorias\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D92ED6-13D0-4937-96C1-4ED2C3C6F51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19610C34-3D21-4C8B-B281-C1E523214893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="14700" activeTab="1" xr2:uid="{AF714EF7-3D0F-49B7-815C-B9007B2E34CE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="11640" activeTab="4" xr2:uid="{AF714EF7-3D0F-49B7-815C-B9007B2E34CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Parámetros" sheetId="1" r:id="rId1"/>
-    <sheet name="Ventas" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId2"/>
+    <sheet name="Hoja4" sheetId="4" r:id="rId3"/>
+    <sheet name="Hoja5" sheetId="5" r:id="rId4"/>
+    <sheet name="Hoja6" sheetId="6" r:id="rId5"/>
+    <sheet name="Ventas" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="19" r:id="rId7"/>
+    <pivotCache cacheId="58" r:id="rId8"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="136">
   <si>
     <t>Fecha</t>
   </si>
@@ -387,7 +395,67 @@
     <t>V-1080</t>
   </si>
   <si>
-    <t>Impuest</t>
+    <t>Impuesto</t>
+  </si>
+  <si>
+    <t>Suma de Venta neta</t>
+  </si>
+  <si>
+    <t>Etiquetas de fila</t>
+  </si>
+  <si>
+    <t>Total general</t>
+  </si>
+  <si>
+    <t>Etiquetas de columna</t>
+  </si>
+  <si>
+    <t>ene</t>
+  </si>
+  <si>
+    <t>feb</t>
+  </si>
+  <si>
+    <t>mar</t>
+  </si>
+  <si>
+    <t>abr</t>
+  </si>
+  <si>
+    <t>may</t>
+  </si>
+  <si>
+    <t>jun</t>
+  </si>
+  <si>
+    <t>jul</t>
+  </si>
+  <si>
+    <t>Escenario</t>
+  </si>
+  <si>
+    <t>Conservador</t>
+  </si>
+  <si>
+    <t>$2.080.000</t>
+  </si>
+  <si>
+    <t>Promocional</t>
+  </si>
+  <si>
+    <t>$2.808.000</t>
+  </si>
+  <si>
+    <t>Optimista</t>
+  </si>
+  <si>
+    <t>$3.952.000</t>
+  </si>
+  <si>
+    <t>Concepto</t>
+  </si>
+  <si>
+    <t>Valor</t>
   </si>
 </sst>
 </file>
@@ -398,7 +466,22 @@
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -438,26 +521,58 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -468,6 +583,5778 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[02_BD_Venta_IZIED.xlsx]Hoja3!TablaDinámica15</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Suma de Venta neta por Vendedor</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja3!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja3!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Andrea Soto</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Carlos Rojas</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Javier Muñoz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Luis Pérez</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>María Fuentes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja3!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* "-"\ _€_-;_-@_-</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>53613500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50908400</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23217000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59276800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>59807450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3D58-4762-94EB-986448628F6F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="766155887"/>
+        <c:axId val="766150127"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="766155887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="766150127"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="766150127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="766155887"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Ventas!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Venta neta </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Ventas!$B$2:$B$81</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46029</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46032</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46037</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46039</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46053</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46068</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46070</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46075</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46088</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46102</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46109</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46117</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46124</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46130</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46138</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46144</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46152</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46165</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46170</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46172</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46180</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46192</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46200</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46207</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46209</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46212</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46215</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46218</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46220</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46222</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46224</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Ventas!$K$2:$K$81</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* "-"\ _€_-;_-@_-</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>2080000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>357200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3952000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6080000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>527000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>470000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2327500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>499500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3239500</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4900000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>468000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>263500</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2080000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4200000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1844500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7560000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>803700</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3536000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>476000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1665000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4165000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>136000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>790500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7980000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>589000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2052000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1110000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>520000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8664000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>544000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5168000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7140000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>370000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>710600</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1860000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4900000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>5928000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>8400000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2450000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>710600</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>470000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6498000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>68000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1933250</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>408000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3100000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3040000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8400000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2280000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>6080000</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>494000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>7600000</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4200000</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2205000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>7980000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1757500</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2945000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7980000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2170000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1034000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>4655000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>272000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>61200</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>4862000</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1240000</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2035000</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>7942000</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4900000</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>714400</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>3458000</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7560000</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>57800</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4900000</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>8360000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>883500</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>555000</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>8208000</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1040000</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2480000</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>479400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DC60-4890-A8F6-88E08C5B6635}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1314156351"/>
+        <c:axId val="1314140511"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1314156351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1314140511"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1314140511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1314156351"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>80010</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>156210</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>80010</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46106470-D133-46D5-1C3F-905DA9768EFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>3809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57BFF269-9A05-CACA-40BE-292D1329A479}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="isolis" refreshedDate="46279.870404629626" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="80" xr:uid="{2CD26CBA-7FFC-4EC7-811D-6984640C3A2F}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:K81" sheet="Ventas"/>
+  </cacheSource>
+  <cacheFields count="11">
+    <cacheField name="ID Venta" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Fecha" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-06T00:00:00" maxDate="2026-07-22T00:00:00"/>
+    </cacheField>
+    <cacheField name="Región" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Vendedor" numFmtId="0">
+      <sharedItems count="5">
+        <s v="María Fuentes"/>
+        <s v="Javier Muñoz"/>
+        <s v="Luis Pérez"/>
+        <s v="Carlos Rojas"/>
+        <s v="Andrea Soto"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Categoría" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Producto" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Canal" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Cantidad" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12"/>
+    </cacheField>
+    <cacheField name="Precio unitario" numFmtId="170">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="68000" maxValue="4200000"/>
+    </cacheField>
+    <cacheField name="Descuento" numFmtId="169">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="0.15"/>
+    </cacheField>
+    <cacheField name="Venta neta" numFmtId="170">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="57800" maxValue="8664000"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="isolis" refreshedDate="46279.88210127315" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="81" xr:uid="{9D11E6BD-1D89-46FA-BFA4-43B32A1C4432}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:K1048576" sheet="Ventas"/>
+  </cacheSource>
+  <cacheFields count="13">
+    <cacheField name="ID Venta" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Fecha" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-01-06T00:00:00" maxDate="2026-07-22T00:00:00" count="81">
+        <d v="2026-01-06T00:00:00"/>
+        <d v="2026-01-07T00:00:00"/>
+        <d v="2026-01-10T00:00:00"/>
+        <d v="2026-01-13T00:00:00"/>
+        <d v="2026-01-15T00:00:00"/>
+        <d v="2026-01-17T00:00:00"/>
+        <d v="2026-01-20T00:00:00"/>
+        <d v="2026-01-22T00:00:00"/>
+        <d v="2026-01-26T00:00:00"/>
+        <d v="2026-01-27T00:00:00"/>
+        <d v="2026-01-31T00:00:00"/>
+        <d v="2026-02-02T00:00:00"/>
+        <d v="2026-02-04T00:00:00"/>
+        <d v="2026-02-06T00:00:00"/>
+        <d v="2026-02-10T00:00:00"/>
+        <d v="2026-02-12T00:00:00"/>
+        <d v="2026-02-15T00:00:00"/>
+        <d v="2026-02-17T00:00:00"/>
+        <d v="2026-02-20T00:00:00"/>
+        <d v="2026-02-22T00:00:00"/>
+        <d v="2026-02-24T00:00:00"/>
+        <d v="2026-02-26T00:00:00"/>
+        <d v="2026-03-02T00:00:00"/>
+        <d v="2026-03-04T00:00:00"/>
+        <d v="2026-03-07T00:00:00"/>
+        <d v="2026-03-09T00:00:00"/>
+        <d v="2026-03-12T00:00:00"/>
+        <d v="2026-03-13T00:00:00"/>
+        <d v="2026-03-17T00:00:00"/>
+        <d v="2026-03-19T00:00:00"/>
+        <d v="2026-03-21T00:00:00"/>
+        <d v="2026-03-24T00:00:00"/>
+        <d v="2026-03-27T00:00:00"/>
+        <d v="2026-03-28T00:00:00"/>
+        <d v="2026-03-31T00:00:00"/>
+        <d v="2026-04-03T00:00:00"/>
+        <d v="2026-04-05T00:00:00"/>
+        <d v="2026-04-07T00:00:00"/>
+        <d v="2026-04-10T00:00:00"/>
+        <d v="2026-04-12T00:00:00"/>
+        <d v="2026-04-15T00:00:00"/>
+        <d v="2026-04-18T00:00:00"/>
+        <d v="2026-04-20T00:00:00"/>
+        <d v="2026-04-22T00:00:00"/>
+        <d v="2026-04-26T00:00:00"/>
+        <d v="2026-04-28T00:00:00"/>
+        <d v="2026-04-30T00:00:00"/>
+        <d v="2026-05-02T00:00:00"/>
+        <d v="2026-05-05T00:00:00"/>
+        <d v="2026-05-07T00:00:00"/>
+        <d v="2026-05-10T00:00:00"/>
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-18T00:00:00"/>
+        <d v="2026-05-21T00:00:00"/>
+        <d v="2026-05-23T00:00:00"/>
+        <d v="2026-05-26T00:00:00"/>
+        <d v="2026-05-28T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
+        <d v="2026-06-01T00:00:00"/>
+        <d v="2026-06-05T00:00:00"/>
+        <d v="2026-06-07T00:00:00"/>
+        <d v="2026-06-09T00:00:00"/>
+        <d v="2026-06-12T00:00:00"/>
+        <d v="2026-06-15T00:00:00"/>
+        <d v="2026-06-17T00:00:00"/>
+        <d v="2026-06-19T00:00:00"/>
+        <d v="2026-06-22T00:00:00"/>
+        <d v="2026-06-24T00:00:00"/>
+        <d v="2026-06-27T00:00:00"/>
+        <d v="2026-06-30T00:00:00"/>
+        <d v="2026-07-01T00:00:00"/>
+        <d v="2026-07-04T00:00:00"/>
+        <d v="2026-07-06T00:00:00"/>
+        <d v="2026-07-09T00:00:00"/>
+        <d v="2026-07-12T00:00:00"/>
+        <d v="2026-07-15T00:00:00"/>
+        <d v="2026-07-17T00:00:00"/>
+        <d v="2026-07-19T00:00:00"/>
+        <d v="2026-07-21T00:00:00"/>
+        <m/>
+      </sharedItems>
+      <fieldGroup par="12"/>
+    </cacheField>
+    <cacheField name="Región" numFmtId="0">
+      <sharedItems containsBlank="1" count="5">
+        <s v="Biobío"/>
+        <s v="Metropolitana"/>
+        <s v="Antofagasta"/>
+        <s v="Valparaíso"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Vendedor" numFmtId="0">
+      <sharedItems containsBlank="1" count="6">
+        <s v="María Fuentes"/>
+        <s v="Javier Muñoz"/>
+        <s v="Luis Pérez"/>
+        <s v="Carlos Rojas"/>
+        <s v="Andrea Soto"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Categoría" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Producto" numFmtId="0">
+      <sharedItems containsBlank="1" count="9">
+        <s v="Mantención preventiva"/>
+        <s v="Sensor de temperatura"/>
+        <s v="Quemador de reemplazo"/>
+        <s v="Inspección anual"/>
+        <s v="Caldera Compacta C-50"/>
+        <s v="Válvula de seguridad"/>
+        <s v="Caldera Industrial C-100"/>
+        <s v="Kit de sellos"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Canal" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Cantidad" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="12"/>
+    </cacheField>
+    <cacheField name="Precio unitario" numFmtId="170">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="68000" maxValue="4200000"/>
+    </cacheField>
+    <cacheField name="Descuento" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="0.15"/>
+    </cacheField>
+    <cacheField name="Venta neta" numFmtId="170">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="57800" maxValue="8664000"/>
+    </cacheField>
+    <cacheField name="Días (Fecha)" numFmtId="0" databaseField="0">
+      <fieldGroup base="1">
+        <rangePr groupBy="days" startDate="2026-01-06T00:00:00" endDate="2026-07-22T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;06/01/2026"/>
+          <s v="01-ene"/>
+          <s v="02-ene"/>
+          <s v="03-ene"/>
+          <s v="04-ene"/>
+          <s v="05-ene"/>
+          <s v="06-ene"/>
+          <s v="07-ene"/>
+          <s v="08-ene"/>
+          <s v="09-ene"/>
+          <s v="10-ene"/>
+          <s v="11-ene"/>
+          <s v="12-ene"/>
+          <s v="13-ene"/>
+          <s v="14-ene"/>
+          <s v="15-ene"/>
+          <s v="16-ene"/>
+          <s v="17-ene"/>
+          <s v="18-ene"/>
+          <s v="19-ene"/>
+          <s v="20-ene"/>
+          <s v="21-ene"/>
+          <s v="22-ene"/>
+          <s v="23-ene"/>
+          <s v="24-ene"/>
+          <s v="25-ene"/>
+          <s v="26-ene"/>
+          <s v="27-ene"/>
+          <s v="28-ene"/>
+          <s v="29-ene"/>
+          <s v="30-ene"/>
+          <s v="31-ene"/>
+          <s v="01-feb"/>
+          <s v="02-feb"/>
+          <s v="03-feb"/>
+          <s v="04-feb"/>
+          <s v="05-feb"/>
+          <s v="06-feb"/>
+          <s v="07-feb"/>
+          <s v="08-feb"/>
+          <s v="09-feb"/>
+          <s v="10-feb"/>
+          <s v="11-feb"/>
+          <s v="12-feb"/>
+          <s v="13-feb"/>
+          <s v="14-feb"/>
+          <s v="15-feb"/>
+          <s v="16-feb"/>
+          <s v="17-feb"/>
+          <s v="18-feb"/>
+          <s v="19-feb"/>
+          <s v="20-feb"/>
+          <s v="21-feb"/>
+          <s v="22-feb"/>
+          <s v="23-feb"/>
+          <s v="24-feb"/>
+          <s v="25-feb"/>
+          <s v="26-feb"/>
+          <s v="27-feb"/>
+          <s v="28-feb"/>
+          <s v="29-feb"/>
+          <s v="01-mar"/>
+          <s v="02-mar"/>
+          <s v="03-mar"/>
+          <s v="04-mar"/>
+          <s v="05-mar"/>
+          <s v="06-mar"/>
+          <s v="07-mar"/>
+          <s v="08-mar"/>
+          <s v="09-mar"/>
+          <s v="10-mar"/>
+          <s v="11-mar"/>
+          <s v="12-mar"/>
+          <s v="13-mar"/>
+          <s v="14-mar"/>
+          <s v="15-mar"/>
+          <s v="16-mar"/>
+          <s v="17-mar"/>
+          <s v="18-mar"/>
+          <s v="19-mar"/>
+          <s v="20-mar"/>
+          <s v="21-mar"/>
+          <s v="22-mar"/>
+          <s v="23-mar"/>
+          <s v="24-mar"/>
+          <s v="25-mar"/>
+          <s v="26-mar"/>
+          <s v="27-mar"/>
+          <s v="28-mar"/>
+          <s v="29-mar"/>
+          <s v="30-mar"/>
+          <s v="31-mar"/>
+          <s v="01-abr"/>
+          <s v="02-abr"/>
+          <s v="03-abr"/>
+          <s v="04-abr"/>
+          <s v="05-abr"/>
+          <s v="06-abr"/>
+          <s v="07-abr"/>
+          <s v="08-abr"/>
+          <s v="09-abr"/>
+          <s v="10-abr"/>
+          <s v="11-abr"/>
+          <s v="12-abr"/>
+          <s v="13-abr"/>
+          <s v="14-abr"/>
+          <s v="15-abr"/>
+          <s v="16-abr"/>
+          <s v="17-abr"/>
+          <s v="18-abr"/>
+          <s v="19-abr"/>
+          <s v="20-abr"/>
+          <s v="21-abr"/>
+          <s v="22-abr"/>
+          <s v="23-abr"/>
+          <s v="24-abr"/>
+          <s v="25-abr"/>
+          <s v="26-abr"/>
+          <s v="27-abr"/>
+          <s v="28-abr"/>
+          <s v="29-abr"/>
+          <s v="30-abr"/>
+          <s v="01-may"/>
+          <s v="02-may"/>
+          <s v="03-may"/>
+          <s v="04-may"/>
+          <s v="05-may"/>
+          <s v="06-may"/>
+          <s v="07-may"/>
+          <s v="08-may"/>
+          <s v="09-may"/>
+          <s v="10-may"/>
+          <s v="11-may"/>
+          <s v="12-may"/>
+          <s v="13-may"/>
+          <s v="14-may"/>
+          <s v="15-may"/>
+          <s v="16-may"/>
+          <s v="17-may"/>
+          <s v="18-may"/>
+          <s v="19-may"/>
+          <s v="20-may"/>
+          <s v="21-may"/>
+          <s v="22-may"/>
+          <s v="23-may"/>
+          <s v="24-may"/>
+          <s v="25-may"/>
+          <s v="26-may"/>
+          <s v="27-may"/>
+          <s v="28-may"/>
+          <s v="29-may"/>
+          <s v="30-may"/>
+          <s v="31-may"/>
+          <s v="01-jun"/>
+          <s v="02-jun"/>
+          <s v="03-jun"/>
+          <s v="04-jun"/>
+          <s v="05-jun"/>
+          <s v="06-jun"/>
+          <s v="07-jun"/>
+          <s v="08-jun"/>
+          <s v="09-jun"/>
+          <s v="10-jun"/>
+          <s v="11-jun"/>
+          <s v="12-jun"/>
+          <s v="13-jun"/>
+          <s v="14-jun"/>
+          <s v="15-jun"/>
+          <s v="16-jun"/>
+          <s v="17-jun"/>
+          <s v="18-jun"/>
+          <s v="19-jun"/>
+          <s v="20-jun"/>
+          <s v="21-jun"/>
+          <s v="22-jun"/>
+          <s v="23-jun"/>
+          <s v="24-jun"/>
+          <s v="25-jun"/>
+          <s v="26-jun"/>
+          <s v="27-jun"/>
+          <s v="28-jun"/>
+          <s v="29-jun"/>
+          <s v="30-jun"/>
+          <s v="01-jul"/>
+          <s v="02-jul"/>
+          <s v="03-jul"/>
+          <s v="04-jul"/>
+          <s v="05-jul"/>
+          <s v="06-jul"/>
+          <s v="07-jul"/>
+          <s v="08-jul"/>
+          <s v="09-jul"/>
+          <s v="10-jul"/>
+          <s v="11-jul"/>
+          <s v="12-jul"/>
+          <s v="13-jul"/>
+          <s v="14-jul"/>
+          <s v="15-jul"/>
+          <s v="16-jul"/>
+          <s v="17-jul"/>
+          <s v="18-jul"/>
+          <s v="19-jul"/>
+          <s v="20-jul"/>
+          <s v="21-jul"/>
+          <s v="22-jul"/>
+          <s v="23-jul"/>
+          <s v="24-jul"/>
+          <s v="25-jul"/>
+          <s v="26-jul"/>
+          <s v="27-jul"/>
+          <s v="28-jul"/>
+          <s v="29-jul"/>
+          <s v="30-jul"/>
+          <s v="31-jul"/>
+          <s v="01-ago"/>
+          <s v="02-ago"/>
+          <s v="03-ago"/>
+          <s v="04-ago"/>
+          <s v="05-ago"/>
+          <s v="06-ago"/>
+          <s v="07-ago"/>
+          <s v="08-ago"/>
+          <s v="09-ago"/>
+          <s v="10-ago"/>
+          <s v="11-ago"/>
+          <s v="12-ago"/>
+          <s v="13-ago"/>
+          <s v="14-ago"/>
+          <s v="15-ago"/>
+          <s v="16-ago"/>
+          <s v="17-ago"/>
+          <s v="18-ago"/>
+          <s v="19-ago"/>
+          <s v="20-ago"/>
+          <s v="21-ago"/>
+          <s v="22-ago"/>
+          <s v="23-ago"/>
+          <s v="24-ago"/>
+          <s v="25-ago"/>
+          <s v="26-ago"/>
+          <s v="27-ago"/>
+          <s v="28-ago"/>
+          <s v="29-ago"/>
+          <s v="30-ago"/>
+          <s v="31-ago"/>
+          <s v="01-sep"/>
+          <s v="02-sep"/>
+          <s v="03-sep"/>
+          <s v="04-sep"/>
+          <s v="05-sep"/>
+          <s v="06-sep"/>
+          <s v="07-sep"/>
+          <s v="08-sep"/>
+          <s v="09-sep"/>
+          <s v="10-sep"/>
+          <s v="11-sep"/>
+          <s v="12-sep"/>
+          <s v="13-sep"/>
+          <s v="14-sep"/>
+          <s v="15-sep"/>
+          <s v="16-sep"/>
+          <s v="17-sep"/>
+          <s v="18-sep"/>
+          <s v="19-sep"/>
+          <s v="20-sep"/>
+          <s v="21-sep"/>
+          <s v="22-sep"/>
+          <s v="23-sep"/>
+          <s v="24-sep"/>
+          <s v="25-sep"/>
+          <s v="26-sep"/>
+          <s v="27-sep"/>
+          <s v="28-sep"/>
+          <s v="29-sep"/>
+          <s v="30-sep"/>
+          <s v="01-oct"/>
+          <s v="02-oct"/>
+          <s v="03-oct"/>
+          <s v="04-oct"/>
+          <s v="05-oct"/>
+          <s v="06-oct"/>
+          <s v="07-oct"/>
+          <s v="08-oct"/>
+          <s v="09-oct"/>
+          <s v="10-oct"/>
+          <s v="11-oct"/>
+          <s v="12-oct"/>
+          <s v="13-oct"/>
+          <s v="14-oct"/>
+          <s v="15-oct"/>
+          <s v="16-oct"/>
+          <s v="17-oct"/>
+          <s v="18-oct"/>
+          <s v="19-oct"/>
+          <s v="20-oct"/>
+          <s v="21-oct"/>
+          <s v="22-oct"/>
+          <s v="23-oct"/>
+          <s v="24-oct"/>
+          <s v="25-oct"/>
+          <s v="26-oct"/>
+          <s v="27-oct"/>
+          <s v="28-oct"/>
+          <s v="29-oct"/>
+          <s v="30-oct"/>
+          <s v="31-oct"/>
+          <s v="01-nov"/>
+          <s v="02-nov"/>
+          <s v="03-nov"/>
+          <s v="04-nov"/>
+          <s v="05-nov"/>
+          <s v="06-nov"/>
+          <s v="07-nov"/>
+          <s v="08-nov"/>
+          <s v="09-nov"/>
+          <s v="10-nov"/>
+          <s v="11-nov"/>
+          <s v="12-nov"/>
+          <s v="13-nov"/>
+          <s v="14-nov"/>
+          <s v="15-nov"/>
+          <s v="16-nov"/>
+          <s v="17-nov"/>
+          <s v="18-nov"/>
+          <s v="19-nov"/>
+          <s v="20-nov"/>
+          <s v="21-nov"/>
+          <s v="22-nov"/>
+          <s v="23-nov"/>
+          <s v="24-nov"/>
+          <s v="25-nov"/>
+          <s v="26-nov"/>
+          <s v="27-nov"/>
+          <s v="28-nov"/>
+          <s v="29-nov"/>
+          <s v="30-nov"/>
+          <s v="01-dic"/>
+          <s v="02-dic"/>
+          <s v="03-dic"/>
+          <s v="04-dic"/>
+          <s v="05-dic"/>
+          <s v="06-dic"/>
+          <s v="07-dic"/>
+          <s v="08-dic"/>
+          <s v="09-dic"/>
+          <s v="10-dic"/>
+          <s v="11-dic"/>
+          <s v="12-dic"/>
+          <s v="13-dic"/>
+          <s v="14-dic"/>
+          <s v="15-dic"/>
+          <s v="16-dic"/>
+          <s v="17-dic"/>
+          <s v="18-dic"/>
+          <s v="19-dic"/>
+          <s v="20-dic"/>
+          <s v="21-dic"/>
+          <s v="22-dic"/>
+          <s v="23-dic"/>
+          <s v="24-dic"/>
+          <s v="25-dic"/>
+          <s v="26-dic"/>
+          <s v="27-dic"/>
+          <s v="28-dic"/>
+          <s v="29-dic"/>
+          <s v="30-dic"/>
+          <s v="31-dic"/>
+          <s v="&gt;22/07/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Meses (Fecha)" numFmtId="0" databaseField="0">
+      <fieldGroup base="1">
+        <rangePr groupBy="months" startDate="2026-01-06T00:00:00" endDate="2026-07-22T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;06/01/2026"/>
+          <s v="ene"/>
+          <s v="feb"/>
+          <s v="mar"/>
+          <s v="abr"/>
+          <s v="may"/>
+          <s v="jun"/>
+          <s v="jul"/>
+          <s v="ago"/>
+          <s v="sep"/>
+          <s v="oct"/>
+          <s v="nov"/>
+          <s v="dic"/>
+          <s v="&gt;22/07/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="1918697963"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="80">
+  <r>
+    <s v="V-1001"/>
+    <d v="2026-01-06T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Directo"/>
+    <n v="4"/>
+    <n v="520000"/>
+    <n v="0"/>
+    <n v="2080000"/>
+  </r>
+  <r>
+    <s v="V-1002"/>
+    <d v="2026-01-07T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="1"/>
+    <s v="Repuestos"/>
+    <s v="Sensor de temperatura"/>
+    <s v="Online"/>
+    <n v="4"/>
+    <n v="94000"/>
+    <n v="0.05"/>
+    <n v="357200"/>
+  </r>
+  <r>
+    <s v="V-1003"/>
+    <d v="2026-01-10T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="520000"/>
+    <n v="0.05"/>
+    <n v="3952000"/>
+  </r>
+  <r>
+    <s v="V-1004"/>
+    <d v="2026-01-13T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="6080000"/>
+  </r>
+  <r>
+    <s v="V-1005"/>
+    <d v="2026-01-15T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="310000"/>
+    <n v="0.15"/>
+    <n v="527000"/>
+  </r>
+  <r>
+    <s v="V-1006"/>
+    <d v="2026-01-17T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <s v="Sensor de temperatura"/>
+    <s v="Distribuidor"/>
+    <n v="5"/>
+    <n v="94000"/>
+    <n v="0"/>
+    <n v="470000"/>
+  </r>
+  <r>
+    <s v="V-1007"/>
+    <d v="2026-01-20T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <s v="Caldera Compacta C-50"/>
+    <s v="Distribuidor"/>
+    <n v="1"/>
+    <n v="2450000"/>
+    <n v="0.05"/>
+    <n v="2327500"/>
+  </r>
+  <r>
+    <s v="V-1008"/>
+    <d v="2026-01-22T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <s v="Válvula de seguridad"/>
+    <s v="Directo"/>
+    <n v="3"/>
+    <n v="185000"/>
+    <n v="0.1"/>
+    <n v="499500"/>
+  </r>
+  <r>
+    <s v="V-1009"/>
+    <d v="2026-01-26T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="310000"/>
+    <n v="0.05"/>
+    <n v="3239500"/>
+  </r>
+  <r>
+    <s v="V-1010"/>
+    <d v="2026-01-27T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <s v="Caldera Compacta C-50"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="4900000"/>
+  </r>
+  <r>
+    <s v="V-1011"/>
+    <d v="2026-01-31T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Online"/>
+    <n v="1"/>
+    <n v="520000"/>
+    <n v="0.1"/>
+    <n v="468000"/>
+  </r>
+  <r>
+    <s v="V-1012"/>
+    <d v="2026-02-02T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Directo"/>
+    <n v="1"/>
+    <n v="310000"/>
+    <n v="0.15"/>
+    <n v="263500"/>
+  </r>
+  <r>
+    <s v="V-1013"/>
+    <d v="2026-02-04T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Online"/>
+    <n v="4"/>
+    <n v="520000"/>
+    <n v="0"/>
+    <n v="2080000"/>
+  </r>
+  <r>
+    <s v="V-1014"/>
+    <d v="2026-02-06T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Distribuidor"/>
+    <n v="1"/>
+    <n v="4200000"/>
+    <n v="0"/>
+    <n v="4200000"/>
+  </r>
+  <r>
+    <s v="V-1015"/>
+    <d v="2026-02-10T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Online"/>
+    <n v="7"/>
+    <n v="310000"/>
+    <n v="0.15"/>
+    <n v="1844500"/>
+  </r>
+  <r>
+    <s v="V-1016"/>
+    <d v="2026-02-12T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.1"/>
+    <n v="7560000"/>
+  </r>
+  <r>
+    <s v="V-1017"/>
+    <d v="2026-02-15T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <s v="Sensor de temperatura"/>
+    <s v="Online"/>
+    <n v="9"/>
+    <n v="94000"/>
+    <n v="0.05"/>
+    <n v="803700"/>
+  </r>
+  <r>
+    <s v="V-1018"/>
+    <d v="2026-02-17T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="4"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="520000"/>
+    <n v="0.15"/>
+    <n v="3536000"/>
+  </r>
+  <r>
+    <s v="V-1019"/>
+    <d v="2026-02-20T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="0"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Online"/>
+    <n v="7"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="476000"/>
+  </r>
+  <r>
+    <s v="V-1020"/>
+    <d v="2026-02-22T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <s v="Válvula de seguridad"/>
+    <s v="Directo"/>
+    <n v="9"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="1665000"/>
+  </r>
+  <r>
+    <s v="V-1021"/>
+    <d v="2026-02-24T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="1"/>
+    <s v="Calderas"/>
+    <s v="Caldera Compacta C-50"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0.15"/>
+    <n v="4165000"/>
+  </r>
+  <r>
+    <s v="V-1022"/>
+    <d v="2026-02-26T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="3"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="136000"/>
+  </r>
+  <r>
+    <s v="V-1023"/>
+    <d v="2026-03-02T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Online"/>
+    <n v="3"/>
+    <n v="310000"/>
+    <n v="0.15"/>
+    <n v="790500"/>
+  </r>
+  <r>
+    <s v="V-1024"/>
+    <d v="2026-03-04T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.05"/>
+    <n v="7980000"/>
+  </r>
+  <r>
+    <s v="V-1025"/>
+    <d v="2026-03-07T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="310000"/>
+    <n v="0.05"/>
+    <n v="589000"/>
+  </r>
+  <r>
+    <s v="V-1026"/>
+    <d v="2026-03-09T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="4"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Distribuidor"/>
+    <n v="3"/>
+    <n v="760000"/>
+    <n v="0.1"/>
+    <n v="2052000"/>
+  </r>
+  <r>
+    <s v="V-1027"/>
+    <d v="2026-03-12T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <s v="Válvula de seguridad"/>
+    <s v="Online"/>
+    <n v="6"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="1110000"/>
+  </r>
+  <r>
+    <s v="V-1028"/>
+    <d v="2026-03-13T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Online"/>
+    <n v="1"/>
+    <n v="520000"/>
+    <n v="0"/>
+    <n v="520000"/>
+  </r>
+  <r>
+    <s v="V-1029"/>
+    <d v="2026-03-17T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Directo"/>
+    <n v="12"/>
+    <n v="760000"/>
+    <n v="0.05"/>
+    <n v="8664000"/>
+  </r>
+  <r>
+    <s v="V-1030"/>
+    <d v="2026-03-19T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="1"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="544000"/>
+  </r>
+  <r>
+    <s v="V-1031"/>
+    <d v="2026-03-21T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="2"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Directo"/>
+    <n v="8"/>
+    <n v="760000"/>
+    <n v="0.15"/>
+    <n v="5168000"/>
+  </r>
+  <r>
+    <s v="V-1032"/>
+    <d v="2026-03-24T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="2"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.15"/>
+    <n v="7140000"/>
+  </r>
+  <r>
+    <s v="V-1033"/>
+    <d v="2026-03-27T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <s v="Válvula de seguridad"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="370000"/>
+  </r>
+  <r>
+    <s v="V-1034"/>
+    <d v="2026-03-28T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="3"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Online"/>
+    <n v="11"/>
+    <n v="68000"/>
+    <n v="0.05"/>
+    <n v="710600"/>
+  </r>
+  <r>
+    <s v="V-1035"/>
+    <d v="2026-03-31T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="4"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Online"/>
+    <n v="6"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="1860000"/>
+  </r>
+  <r>
+    <s v="V-1036"/>
+    <d v="2026-04-03T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <s v="Caldera Compacta C-50"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="4900000"/>
+  </r>
+  <r>
+    <s v="V-1037"/>
+    <d v="2026-04-05T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Online"/>
+    <n v="12"/>
+    <n v="520000"/>
+    <n v="0.05"/>
+    <n v="5928000"/>
+  </r>
+  <r>
+    <s v="V-1038"/>
+    <d v="2026-04-07T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="2"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0"/>
+    <n v="8400000"/>
+  </r>
+  <r>
+    <s v="V-1039"/>
+    <d v="2026-04-10T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <s v="Caldera Compacta C-50"/>
+    <s v="Distribuidor"/>
+    <n v="1"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="2450000"/>
+  </r>
+  <r>
+    <s v="V-1040"/>
+    <d v="2026-04-12T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="3"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Directo"/>
+    <n v="11"/>
+    <n v="68000"/>
+    <n v="0.05"/>
+    <n v="710600"/>
+  </r>
+  <r>
+    <s v="V-1041"/>
+    <d v="2026-04-15T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <s v="Sensor de temperatura"/>
+    <s v="Distribuidor"/>
+    <n v="5"/>
+    <n v="94000"/>
+    <n v="0"/>
+    <n v="470000"/>
+  </r>
+  <r>
+    <s v="V-1042"/>
+    <d v="2026-04-18T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="2"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Distribuidor"/>
+    <n v="9"/>
+    <n v="760000"/>
+    <n v="0.05"/>
+    <n v="6498000"/>
+  </r>
+  <r>
+    <s v="V-1043"/>
+    <d v="2026-04-20T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="0"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Directo"/>
+    <n v="1"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="68000"/>
+  </r>
+  <r>
+    <s v="V-1044"/>
+    <d v="2026-04-22T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <s v="Válvula de seguridad"/>
+    <s v="Directo"/>
+    <n v="11"/>
+    <n v="185000"/>
+    <n v="0.05"/>
+    <n v="1933250"/>
+  </r>
+  <r>
+    <s v="V-1045"/>
+    <d v="2026-04-26T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="0"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Online"/>
+    <n v="6"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="408000"/>
+  </r>
+  <r>
+    <s v="V-1046"/>
+    <d v="2026-04-28T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Distribuidor"/>
+    <n v="10"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="3100000"/>
+  </r>
+  <r>
+    <s v="V-1047"/>
+    <d v="2026-04-30T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="2"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Online"/>
+    <n v="4"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="3040000"/>
+  </r>
+  <r>
+    <s v="V-1048"/>
+    <d v="2026-05-02T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0"/>
+    <n v="8400000"/>
+  </r>
+  <r>
+    <s v="V-1049"/>
+    <d v="2026-05-05T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="2"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Distribuidor"/>
+    <n v="3"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="2280000"/>
+  </r>
+  <r>
+    <s v="V-1050"/>
+    <d v="2026-05-07T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Directo"/>
+    <n v="8"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="6080000"/>
+  </r>
+  <r>
+    <s v="V-1051"/>
+    <d v="2026-05-10T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Distribuidor"/>
+    <n v="1"/>
+    <n v="520000"/>
+    <n v="0.05"/>
+    <n v="494000"/>
+  </r>
+  <r>
+    <s v="V-1052"/>
+    <d v="2026-05-12T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="4"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Online"/>
+    <n v="10"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="7600000"/>
+  </r>
+  <r>
+    <s v="V-1053"/>
+    <d v="2026-05-15T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="3"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Online"/>
+    <n v="1"/>
+    <n v="4200000"/>
+    <n v="0"/>
+    <n v="4200000"/>
+  </r>
+  <r>
+    <s v="V-1054"/>
+    <d v="2026-05-18T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <s v="Caldera Compacta C-50"/>
+    <s v="Directo"/>
+    <n v="1"/>
+    <n v="2450000"/>
+    <n v="0.1"/>
+    <n v="2205000"/>
+  </r>
+  <r>
+    <s v="V-1055"/>
+    <d v="2026-05-21T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="3"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.05"/>
+    <n v="7980000"/>
+  </r>
+  <r>
+    <s v="V-1056"/>
+    <d v="2026-05-23T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <s v="Válvula de seguridad"/>
+    <s v="Online"/>
+    <n v="10"/>
+    <n v="185000"/>
+    <n v="0.05"/>
+    <n v="1757500"/>
+  </r>
+  <r>
+    <s v="V-1057"/>
+    <d v="2026-05-26T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Online"/>
+    <n v="10"/>
+    <n v="310000"/>
+    <n v="0.05"/>
+    <n v="2945000"/>
+  </r>
+  <r>
+    <s v="V-1058"/>
+    <d v="2026-05-28T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="2"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.05"/>
+    <n v="7980000"/>
+  </r>
+  <r>
+    <s v="V-1059"/>
+    <d v="2026-05-30T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Directo"/>
+    <n v="7"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="2170000"/>
+  </r>
+  <r>
+    <s v="V-1060"/>
+    <d v="2026-06-01T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="4"/>
+    <s v="Repuestos"/>
+    <s v="Sensor de temperatura"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="94000"/>
+    <n v="0"/>
+    <n v="1034000"/>
+  </r>
+  <r>
+    <s v="V-1061"/>
+    <d v="2026-06-05T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="1"/>
+    <s v="Calderas"/>
+    <s v="Caldera Compacta C-50"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0.05"/>
+    <n v="4655000"/>
+  </r>
+  <r>
+    <s v="V-1062"/>
+    <d v="2026-06-07T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="0"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Distribuidor"/>
+    <n v="4"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="272000"/>
+  </r>
+  <r>
+    <s v="V-1063"/>
+    <d v="2026-06-09T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="3"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Online"/>
+    <n v="1"/>
+    <n v="68000"/>
+    <n v="0.1"/>
+    <n v="61200"/>
+  </r>
+  <r>
+    <s v="V-1064"/>
+    <d v="2026-06-12T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="4"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="520000"/>
+    <n v="0.15"/>
+    <n v="4862000"/>
+  </r>
+  <r>
+    <s v="V-1065"/>
+    <d v="2026-06-15T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Directo"/>
+    <n v="4"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="1240000"/>
+  </r>
+  <r>
+    <s v="V-1066"/>
+    <d v="2026-06-17T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="1"/>
+    <s v="Repuestos"/>
+    <s v="Válvula de seguridad"/>
+    <s v="Online"/>
+    <n v="11"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="2035000"/>
+  </r>
+  <r>
+    <s v="V-1067"/>
+    <d v="2026-06-19T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="4"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="760000"/>
+    <n v="0.05"/>
+    <n v="7942000"/>
+  </r>
+  <r>
+    <s v="V-1068"/>
+    <d v="2026-06-22T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="2"/>
+    <s v="Calderas"/>
+    <s v="Caldera Compacta C-50"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="4900000"/>
+  </r>
+  <r>
+    <s v="V-1069"/>
+    <d v="2026-06-24T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="1"/>
+    <s v="Repuestos"/>
+    <s v="Sensor de temperatura"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="94000"/>
+    <n v="0.05"/>
+    <n v="714400"/>
+  </r>
+  <r>
+    <s v="V-1070"/>
+    <d v="2026-06-27T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Online"/>
+    <n v="7"/>
+    <n v="520000"/>
+    <n v="0.05"/>
+    <n v="3458000"/>
+  </r>
+  <r>
+    <s v="V-1071"/>
+    <d v="2026-06-30T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <s v="Caldera Industrial C-100"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.1"/>
+    <n v="7560000"/>
+  </r>
+  <r>
+    <s v="V-1072"/>
+    <d v="2026-07-01T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="2"/>
+    <s v="Insumos"/>
+    <s v="Kit de sellos"/>
+    <s v="Directo"/>
+    <n v="1"/>
+    <n v="68000"/>
+    <n v="0.15"/>
+    <n v="57800"/>
+  </r>
+  <r>
+    <s v="V-1073"/>
+    <d v="2026-07-04T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <s v="Caldera Compacta C-50"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="4900000"/>
+  </r>
+  <r>
+    <s v="V-1074"/>
+    <d v="2026-07-06T00:00:00"/>
+    <s v="Metropolitana"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="8360000"/>
+  </r>
+  <r>
+    <s v="V-1075"/>
+    <d v="2026-07-09T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Online"/>
+    <n v="3"/>
+    <n v="310000"/>
+    <n v="0.05"/>
+    <n v="883500"/>
+  </r>
+  <r>
+    <s v="V-1076"/>
+    <d v="2026-07-12T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <s v="Válvula de seguridad"/>
+    <s v="Online"/>
+    <n v="3"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="555000"/>
+  </r>
+  <r>
+    <s v="V-1077"/>
+    <d v="2026-07-15T00:00:00"/>
+    <s v="Antofagasta"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <s v="Quemador de reemplazo"/>
+    <s v="Online"/>
+    <n v="12"/>
+    <n v="760000"/>
+    <n v="0.1"/>
+    <n v="8208000"/>
+  </r>
+  <r>
+    <s v="V-1078"/>
+    <d v="2026-07-17T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <s v="Mantención preventiva"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="520000"/>
+    <n v="0"/>
+    <n v="1040000"/>
+  </r>
+  <r>
+    <s v="V-1079"/>
+    <d v="2026-07-19T00:00:00"/>
+    <s v="Biobío"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <s v="Inspección anual"/>
+    <s v="Distribuidor"/>
+    <n v="8"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="2480000"/>
+  </r>
+  <r>
+    <s v="V-1080"/>
+    <d v="2026-07-21T00:00:00"/>
+    <s v="Valparaíso"/>
+    <x v="1"/>
+    <s v="Repuestos"/>
+    <s v="Sensor de temperatura"/>
+    <s v="Online"/>
+    <n v="6"/>
+    <n v="94000"/>
+    <n v="0.15"/>
+    <n v="479400"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="81">
+  <r>
+    <s v="V-1001"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Directo"/>
+    <n v="4"/>
+    <n v="520000"/>
+    <n v="0"/>
+    <n v="2080000"/>
+  </r>
+  <r>
+    <s v="V-1002"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Repuestos"/>
+    <x v="1"/>
+    <s v="Online"/>
+    <n v="4"/>
+    <n v="94000"/>
+    <n v="0.05"/>
+    <n v="357200"/>
+  </r>
+  <r>
+    <s v="V-1003"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="520000"/>
+    <n v="0.05"/>
+    <n v="3952000"/>
+  </r>
+  <r>
+    <s v="V-1004"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="6080000"/>
+  </r>
+  <r>
+    <s v="V-1005"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="310000"/>
+    <n v="0.15"/>
+    <n v="527000"/>
+  </r>
+  <r>
+    <s v="V-1006"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <x v="1"/>
+    <s v="Distribuidor"/>
+    <n v="5"/>
+    <n v="94000"/>
+    <n v="0"/>
+    <n v="470000"/>
+  </r>
+  <r>
+    <s v="V-1007"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <x v="4"/>
+    <s v="Distribuidor"/>
+    <n v="1"/>
+    <n v="2450000"/>
+    <n v="0.05"/>
+    <n v="2327500"/>
+  </r>
+  <r>
+    <s v="V-1008"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <x v="5"/>
+    <s v="Directo"/>
+    <n v="3"/>
+    <n v="185000"/>
+    <n v="0.1"/>
+    <n v="499500"/>
+  </r>
+  <r>
+    <s v="V-1009"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="310000"/>
+    <n v="0.05"/>
+    <n v="3239500"/>
+  </r>
+  <r>
+    <s v="V-1010"/>
+    <x v="9"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <x v="4"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="4900000"/>
+  </r>
+  <r>
+    <s v="V-1011"/>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Online"/>
+    <n v="1"/>
+    <n v="520000"/>
+    <n v="0.1"/>
+    <n v="468000"/>
+  </r>
+  <r>
+    <s v="V-1012"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Directo"/>
+    <n v="1"/>
+    <n v="310000"/>
+    <n v="0.15"/>
+    <n v="263500"/>
+  </r>
+  <r>
+    <s v="V-1013"/>
+    <x v="12"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Online"/>
+    <n v="4"/>
+    <n v="520000"/>
+    <n v="0"/>
+    <n v="2080000"/>
+  </r>
+  <r>
+    <s v="V-1014"/>
+    <x v="13"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Distribuidor"/>
+    <n v="1"/>
+    <n v="4200000"/>
+    <n v="0"/>
+    <n v="4200000"/>
+  </r>
+  <r>
+    <s v="V-1015"/>
+    <x v="14"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Online"/>
+    <n v="7"/>
+    <n v="310000"/>
+    <n v="0.15"/>
+    <n v="1844500"/>
+  </r>
+  <r>
+    <s v="V-1016"/>
+    <x v="15"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.1"/>
+    <n v="7560000"/>
+  </r>
+  <r>
+    <s v="V-1017"/>
+    <x v="16"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <x v="1"/>
+    <s v="Online"/>
+    <n v="9"/>
+    <n v="94000"/>
+    <n v="0.05"/>
+    <n v="803700"/>
+  </r>
+  <r>
+    <s v="V-1018"/>
+    <x v="17"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="520000"/>
+    <n v="0.15"/>
+    <n v="3536000"/>
+  </r>
+  <r>
+    <s v="V-1019"/>
+    <x v="18"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Online"/>
+    <n v="7"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="476000"/>
+  </r>
+  <r>
+    <s v="V-1020"/>
+    <x v="19"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <x v="5"/>
+    <s v="Directo"/>
+    <n v="9"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="1665000"/>
+  </r>
+  <r>
+    <s v="V-1021"/>
+    <x v="20"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Calderas"/>
+    <x v="4"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0.15"/>
+    <n v="4165000"/>
+  </r>
+  <r>
+    <s v="V-1022"/>
+    <x v="21"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="136000"/>
+  </r>
+  <r>
+    <s v="V-1023"/>
+    <x v="22"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Online"/>
+    <n v="3"/>
+    <n v="310000"/>
+    <n v="0.15"/>
+    <n v="790500"/>
+  </r>
+  <r>
+    <s v="V-1024"/>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.05"/>
+    <n v="7980000"/>
+  </r>
+  <r>
+    <s v="V-1025"/>
+    <x v="24"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="310000"/>
+    <n v="0.05"/>
+    <n v="589000"/>
+  </r>
+  <r>
+    <s v="V-1026"/>
+    <x v="25"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Distribuidor"/>
+    <n v="3"/>
+    <n v="760000"/>
+    <n v="0.1"/>
+    <n v="2052000"/>
+  </r>
+  <r>
+    <s v="V-1027"/>
+    <x v="26"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <x v="5"/>
+    <s v="Online"/>
+    <n v="6"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="1110000"/>
+  </r>
+  <r>
+    <s v="V-1028"/>
+    <x v="27"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Online"/>
+    <n v="1"/>
+    <n v="520000"/>
+    <n v="0"/>
+    <n v="520000"/>
+  </r>
+  <r>
+    <s v="V-1029"/>
+    <x v="28"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Directo"/>
+    <n v="12"/>
+    <n v="760000"/>
+    <n v="0.05"/>
+    <n v="8664000"/>
+  </r>
+  <r>
+    <s v="V-1030"/>
+    <x v="29"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="544000"/>
+  </r>
+  <r>
+    <s v="V-1031"/>
+    <x v="30"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Directo"/>
+    <n v="8"/>
+    <n v="760000"/>
+    <n v="0.15"/>
+    <n v="5168000"/>
+  </r>
+  <r>
+    <s v="V-1032"/>
+    <x v="31"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.15"/>
+    <n v="7140000"/>
+  </r>
+  <r>
+    <s v="V-1033"/>
+    <x v="32"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <x v="5"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="370000"/>
+  </r>
+  <r>
+    <s v="V-1034"/>
+    <x v="33"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Online"/>
+    <n v="11"/>
+    <n v="68000"/>
+    <n v="0.05"/>
+    <n v="710600"/>
+  </r>
+  <r>
+    <s v="V-1035"/>
+    <x v="34"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Online"/>
+    <n v="6"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="1860000"/>
+  </r>
+  <r>
+    <s v="V-1036"/>
+    <x v="35"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <x v="4"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="4900000"/>
+  </r>
+  <r>
+    <s v="V-1037"/>
+    <x v="36"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Online"/>
+    <n v="12"/>
+    <n v="520000"/>
+    <n v="0.05"/>
+    <n v="5928000"/>
+  </r>
+  <r>
+    <s v="V-1038"/>
+    <x v="37"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0"/>
+    <n v="8400000"/>
+  </r>
+  <r>
+    <s v="V-1039"/>
+    <x v="38"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <x v="4"/>
+    <s v="Distribuidor"/>
+    <n v="1"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="2450000"/>
+  </r>
+  <r>
+    <s v="V-1040"/>
+    <x v="39"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Directo"/>
+    <n v="11"/>
+    <n v="68000"/>
+    <n v="0.05"/>
+    <n v="710600"/>
+  </r>
+  <r>
+    <s v="V-1041"/>
+    <x v="40"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <x v="1"/>
+    <s v="Distribuidor"/>
+    <n v="5"/>
+    <n v="94000"/>
+    <n v="0"/>
+    <n v="470000"/>
+  </r>
+  <r>
+    <s v="V-1042"/>
+    <x v="41"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Distribuidor"/>
+    <n v="9"/>
+    <n v="760000"/>
+    <n v="0.05"/>
+    <n v="6498000"/>
+  </r>
+  <r>
+    <s v="V-1043"/>
+    <x v="42"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Directo"/>
+    <n v="1"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="68000"/>
+  </r>
+  <r>
+    <s v="V-1044"/>
+    <x v="43"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <x v="5"/>
+    <s v="Directo"/>
+    <n v="11"/>
+    <n v="185000"/>
+    <n v="0.05"/>
+    <n v="1933250"/>
+  </r>
+  <r>
+    <s v="V-1045"/>
+    <x v="44"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Online"/>
+    <n v="6"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="408000"/>
+  </r>
+  <r>
+    <s v="V-1046"/>
+    <x v="45"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Distribuidor"/>
+    <n v="10"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="3100000"/>
+  </r>
+  <r>
+    <s v="V-1047"/>
+    <x v="46"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Online"/>
+    <n v="4"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="3040000"/>
+  </r>
+  <r>
+    <s v="V-1048"/>
+    <x v="47"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0"/>
+    <n v="8400000"/>
+  </r>
+  <r>
+    <s v="V-1049"/>
+    <x v="48"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Distribuidor"/>
+    <n v="3"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="2280000"/>
+  </r>
+  <r>
+    <s v="V-1050"/>
+    <x v="49"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Directo"/>
+    <n v="8"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="6080000"/>
+  </r>
+  <r>
+    <s v="V-1051"/>
+    <x v="50"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Distribuidor"/>
+    <n v="1"/>
+    <n v="520000"/>
+    <n v="0.05"/>
+    <n v="494000"/>
+  </r>
+  <r>
+    <s v="V-1052"/>
+    <x v="51"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Online"/>
+    <n v="10"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="7600000"/>
+  </r>
+  <r>
+    <s v="V-1053"/>
+    <x v="52"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Online"/>
+    <n v="1"/>
+    <n v="4200000"/>
+    <n v="0"/>
+    <n v="4200000"/>
+  </r>
+  <r>
+    <s v="V-1054"/>
+    <x v="53"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <x v="4"/>
+    <s v="Directo"/>
+    <n v="1"/>
+    <n v="2450000"/>
+    <n v="0.1"/>
+    <n v="2205000"/>
+  </r>
+  <r>
+    <s v="V-1055"/>
+    <x v="54"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Directo"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.05"/>
+    <n v="7980000"/>
+  </r>
+  <r>
+    <s v="V-1056"/>
+    <x v="55"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <x v="5"/>
+    <s v="Online"/>
+    <n v="10"/>
+    <n v="185000"/>
+    <n v="0.05"/>
+    <n v="1757500"/>
+  </r>
+  <r>
+    <s v="V-1057"/>
+    <x v="56"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Online"/>
+    <n v="10"/>
+    <n v="310000"/>
+    <n v="0.05"/>
+    <n v="2945000"/>
+  </r>
+  <r>
+    <s v="V-1058"/>
+    <x v="57"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.05"/>
+    <n v="7980000"/>
+  </r>
+  <r>
+    <s v="V-1059"/>
+    <x v="58"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Directo"/>
+    <n v="7"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="2170000"/>
+  </r>
+  <r>
+    <s v="V-1060"/>
+    <x v="59"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="Repuestos"/>
+    <x v="1"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="94000"/>
+    <n v="0"/>
+    <n v="1034000"/>
+  </r>
+  <r>
+    <s v="V-1061"/>
+    <x v="60"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Calderas"/>
+    <x v="4"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0.05"/>
+    <n v="4655000"/>
+  </r>
+  <r>
+    <s v="V-1062"/>
+    <x v="61"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Distribuidor"/>
+    <n v="4"/>
+    <n v="68000"/>
+    <n v="0"/>
+    <n v="272000"/>
+  </r>
+  <r>
+    <s v="V-1063"/>
+    <x v="62"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Online"/>
+    <n v="1"/>
+    <n v="68000"/>
+    <n v="0.1"/>
+    <n v="61200"/>
+  </r>
+  <r>
+    <s v="V-1064"/>
+    <x v="63"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="520000"/>
+    <n v="0.15"/>
+    <n v="4862000"/>
+  </r>
+  <r>
+    <s v="V-1065"/>
+    <x v="64"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Directo"/>
+    <n v="4"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="1240000"/>
+  </r>
+  <r>
+    <s v="V-1066"/>
+    <x v="65"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Repuestos"/>
+    <x v="5"/>
+    <s v="Online"/>
+    <n v="11"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="2035000"/>
+  </r>
+  <r>
+    <s v="V-1067"/>
+    <x v="66"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="760000"/>
+    <n v="0.05"/>
+    <n v="7942000"/>
+  </r>
+  <r>
+    <s v="V-1068"/>
+    <x v="67"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Calderas"/>
+    <x v="4"/>
+    <s v="Online"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="4900000"/>
+  </r>
+  <r>
+    <s v="V-1069"/>
+    <x v="68"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Repuestos"/>
+    <x v="1"/>
+    <s v="Online"/>
+    <n v="8"/>
+    <n v="94000"/>
+    <n v="0.05"/>
+    <n v="714400"/>
+  </r>
+  <r>
+    <s v="V-1070"/>
+    <x v="69"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Online"/>
+    <n v="7"/>
+    <n v="520000"/>
+    <n v="0.05"/>
+    <n v="3458000"/>
+  </r>
+  <r>
+    <s v="V-1071"/>
+    <x v="70"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Calderas"/>
+    <x v="6"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="4200000"/>
+    <n v="0.1"/>
+    <n v="7560000"/>
+  </r>
+  <r>
+    <s v="V-1072"/>
+    <x v="71"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Insumos"/>
+    <x v="7"/>
+    <s v="Directo"/>
+    <n v="1"/>
+    <n v="68000"/>
+    <n v="0.15"/>
+    <n v="57800"/>
+  </r>
+  <r>
+    <s v="V-1073"/>
+    <x v="72"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="Calderas"/>
+    <x v="4"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="2450000"/>
+    <n v="0"/>
+    <n v="4900000"/>
+  </r>
+  <r>
+    <s v="V-1074"/>
+    <x v="73"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Distribuidor"/>
+    <n v="11"/>
+    <n v="760000"/>
+    <n v="0"/>
+    <n v="8360000"/>
+  </r>
+  <r>
+    <s v="V-1075"/>
+    <x v="74"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Online"/>
+    <n v="3"/>
+    <n v="310000"/>
+    <n v="0.05"/>
+    <n v="883500"/>
+  </r>
+  <r>
+    <s v="V-1076"/>
+    <x v="75"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Repuestos"/>
+    <x v="5"/>
+    <s v="Online"/>
+    <n v="3"/>
+    <n v="185000"/>
+    <n v="0"/>
+    <n v="555000"/>
+  </r>
+  <r>
+    <s v="V-1077"/>
+    <x v="76"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Repuestos"/>
+    <x v="2"/>
+    <s v="Online"/>
+    <n v="12"/>
+    <n v="760000"/>
+    <n v="0.1"/>
+    <n v="8208000"/>
+  </r>
+  <r>
+    <s v="V-1078"/>
+    <x v="77"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Servicios"/>
+    <x v="0"/>
+    <s v="Distribuidor"/>
+    <n v="2"/>
+    <n v="520000"/>
+    <n v="0"/>
+    <n v="1040000"/>
+  </r>
+  <r>
+    <s v="V-1079"/>
+    <x v="78"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Servicios"/>
+    <x v="3"/>
+    <s v="Distribuidor"/>
+    <n v="8"/>
+    <n v="310000"/>
+    <n v="0"/>
+    <n v="2480000"/>
+  </r>
+  <r>
+    <s v="V-1080"/>
+    <x v="79"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Repuestos"/>
+    <x v="1"/>
+    <s v="Online"/>
+    <n v="6"/>
+    <n v="94000"/>
+    <n v="0.15"/>
+    <n v="479400"/>
+  </r>
+  <r>
+    <m/>
+    <x v="80"/>
+    <x v="4"/>
+    <x v="5"/>
+    <m/>
+    <x v="8"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E3AE3D3-3AE0-4FF6-90C3-EF3E70E6956A}" name="TablaDinámica15" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="5">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" numFmtId="3" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" numFmtId="170" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" numFmtId="169" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField dataField="1" compact="0" numFmtId="170" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Venta neta" fld="10" baseField="0" baseItem="0" numFmtId="170"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B3A20DDE-905B-4AAA-9023-26A89A645123}" name="TablaDinámica44" cacheId="58" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:I11" firstHeaderRow="1" firstDataRow="4" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="82">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item h="1" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="4"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="3">
+    <field x="12"/>
+    <field x="11"/>
+    <field x="1"/>
+  </colFields>
+  <colItems count="8">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Venta neta" fld="10" baseField="0" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -787,7 +6674,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="5">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="9">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
   <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
@@ -802,7 +6689,9 @@
   <we:alternateReferences>
     <we:reference id="WA200010215" version="2.0.0.0" store="WA200010215" storeType="OMEX"/>
   </we:alternateReferences>
-  <we:properties/>
+  <we:properties>
+    <we:property name="bps.codex_control.document_id" value="&quot;56f6081c-84ff-4a6b-986e-837aacd9cb15&quot;"/>
+  </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </we:webextension>
@@ -824,30 +6713,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E62309-7C03-4AC0-80D7-3A4A25FAF1DD}">
-  <dimension ref="D1:D2"/>
+  <dimension ref="B1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
     <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="30.42578125" customWidth="1"/>
     <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1" t="s">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D2">
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2">
         <v>0.19</v>
+      </c>
+      <c r="H2" s="9">
+        <v>2080000</v>
+      </c>
+      <c r="J2" s="9">
+        <f>SUM(H2:H7)</f>
+        <v>13466200</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H3" s="9">
+        <v>357200</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H4" s="9">
+        <v>3952000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H5" s="9">
+        <v>6080000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="9">
+        <v>527000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H7" s="9">
+        <v>470000</v>
       </c>
     </row>
   </sheetData>
@@ -856,6 +6779,442 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56EF613D-17DB-4A0B-AD4F-F1243D61948D}">
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11">
+        <v>53613500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="11">
+        <v>50908400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="11">
+        <v>23217000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="11">
+        <v>59276800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="11">
+        <v>59807450</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82375BA7-5D27-4024-9712-352CD6CF80CC}">
+  <dimension ref="A3:I11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="81" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="9">
+        <v>5867500</v>
+      </c>
+      <c r="C7" s="9">
+        <v>6092000</v>
+      </c>
+      <c r="D7" s="9">
+        <v>10294000</v>
+      </c>
+      <c r="E7" s="9">
+        <v>14298000</v>
+      </c>
+      <c r="F7" s="9">
+        <v>11099000</v>
+      </c>
+      <c r="G7" s="9">
+        <v>6206000</v>
+      </c>
+      <c r="H7" s="9">
+        <v>13108000</v>
+      </c>
+      <c r="I7" s="9">
+        <v>66964500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="9">
+        <v>8160000</v>
+      </c>
+      <c r="C8" s="9">
+        <v>13653500</v>
+      </c>
+      <c r="D8" s="9">
+        <v>3212500</v>
+      </c>
+      <c r="E8" s="9">
+        <v>12964000</v>
+      </c>
+      <c r="F8" s="9">
+        <v>5957500</v>
+      </c>
+      <c r="G8" s="9">
+        <v>5493000</v>
+      </c>
+      <c r="H8" s="9">
+        <v>3092800</v>
+      </c>
+      <c r="I8" s="9">
+        <v>52533300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="9">
+        <v>7633700</v>
+      </c>
+      <c r="C9" s="9">
+        <v>136000</v>
+      </c>
+      <c r="D9" s="9">
+        <v>22858600</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3100000</v>
+      </c>
+      <c r="F9" s="9">
+        <v>34755000</v>
+      </c>
+      <c r="G9" s="9">
+        <v>18378200</v>
+      </c>
+      <c r="H9" s="9">
+        <v>8360000</v>
+      </c>
+      <c r="I9" s="9">
+        <v>95221500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="9">
+        <v>3239500</v>
+      </c>
+      <c r="C10" s="9">
+        <v>6848200</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1133000</v>
+      </c>
+      <c r="E10" s="9">
+        <v>7543850</v>
+      </c>
+      <c r="F10" s="9">
+        <v>2280000</v>
+      </c>
+      <c r="G10" s="9">
+        <v>8656400</v>
+      </c>
+      <c r="H10" s="9">
+        <v>2402900</v>
+      </c>
+      <c r="I10" s="9">
+        <v>32103850</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="9">
+        <v>24900700</v>
+      </c>
+      <c r="C11" s="9">
+        <v>26729700</v>
+      </c>
+      <c r="D11" s="9">
+        <v>37498100</v>
+      </c>
+      <c r="E11" s="9">
+        <v>37905850</v>
+      </c>
+      <c r="F11" s="9">
+        <v>54091500</v>
+      </c>
+      <c r="G11" s="9">
+        <v>38733600</v>
+      </c>
+      <c r="H11" s="9">
+        <v>26963700</v>
+      </c>
+      <c r="I11" s="9">
+        <v>246823150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F550476-4C46-4B34-9691-D98AE33B6AAC}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="15">
+        <v>520000</v>
+      </c>
+      <c r="G2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2" s="14">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="G3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2">
+        <f>B1*B2*(1-B3)</f>
+        <v>3952000</v>
+      </c>
+      <c r="G4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4" s="14">
+        <v>0.05</v>
+      </c>
+      <c r="J4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <scenarios current="2" show="2">
+    <scenario name="Conservador" locked="1" count="3" user="isolis" comment="Creado por isolis el 14/09/2026">
+      <inputCells r="B1" val="4"/>
+      <inputCells r="B2" val="520000" numFmtId="3"/>
+      <inputCells r="B3" val="0" numFmtId="9"/>
+    </scenario>
+    <scenario name="Promocional" locked="1" count="3" user="isolis" comment="Creado por isolis el 14/09/2026">
+      <inputCells r="B1" val="6"/>
+      <inputCells r="B2" val="520000" numFmtId="3"/>
+      <inputCells r="B3" val="0,1" numFmtId="9"/>
+    </scenario>
+    <scenario name="Optimista" locked="1" count="3" user="isolis" comment="Creado por isolis el 14/09/2026">
+      <inputCells r="B1" val="8"/>
+      <inputCells r="B2" val="520000" numFmtId="3"/>
+      <inputCells r="B3" val="0,05" numFmtId="9"/>
+    </scenario>
+  </scenarios>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{913E73FC-7B4D-4EFF-8171-50511F78CCB2}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5.7692307692307692</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2">
+        <v>520000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2">
+        <f>B2*B3*(1-B4)</f>
+        <v>3000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBB2D0A-A8E3-43EF-BD93-8ABAB70BD408}">
   <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -867,44 +7226,44 @@
     <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -912,7 +7271,7 @@
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <v>46028</v>
       </c>
       <c r="C2" t="s">
@@ -930,33 +7289,27 @@
       <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="9">
         <v>4</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>520000</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="8">
         <v>0</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="11">
         <f>H2*I2*(1-J2)</f>
         <v>2080000</v>
       </c>
-      <c r="L2" s="6">
-        <f>K2*Parámetros!D2</f>
-        <v>395200</v>
-      </c>
-      <c r="M2" s="6">
-        <f>K2+L2</f>
-        <v>2475200</v>
-      </c>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <v>46029</v>
       </c>
       <c r="C3" t="s">
@@ -974,16 +7327,16 @@
       <c r="G3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="9">
         <v>4</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="11">
         <v>94000</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="8">
         <v>0.05</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="11">
         <f t="shared" ref="K3:K66" si="0">H3*I3*(1-J3)</f>
         <v>357200</v>
       </c>
@@ -992,7 +7345,7 @@
       <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="7">
         <v>46032</v>
       </c>
       <c r="C4" t="s">
@@ -1010,16 +7363,16 @@
       <c r="G4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="9">
         <v>8</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="11">
         <v>520000</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="8">
         <v>0.05</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="11">
         <f t="shared" si="0"/>
         <v>3952000</v>
       </c>
@@ -1028,7 +7381,7 @@
       <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <v>46035</v>
       </c>
       <c r="C5" t="s">
@@ -1046,16 +7399,16 @@
       <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="9">
         <v>8</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="11">
         <v>760000</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="8">
         <v>0</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="11">
         <f t="shared" si="0"/>
         <v>6080000</v>
       </c>
@@ -1064,7 +7417,7 @@
       <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="7">
         <v>46037</v>
       </c>
       <c r="C6" t="s">
@@ -1082,16 +7435,16 @@
       <c r="G6" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="9">
         <v>2</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="11">
         <v>310000</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="8">
         <v>0.15</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="11">
         <f t="shared" si="0"/>
         <v>527000</v>
       </c>
@@ -1100,7 +7453,7 @@
       <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="7">
         <v>46039</v>
       </c>
       <c r="C7" t="s">
@@ -1118,16 +7471,16 @@
       <c r="G7" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="9">
         <v>5</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="11">
         <v>94000</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="8">
         <v>0</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="11">
         <f t="shared" si="0"/>
         <v>470000</v>
       </c>
@@ -1136,7 +7489,7 @@
       <c r="A8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <v>46042</v>
       </c>
       <c r="C8" t="s">
@@ -1154,16 +7507,16 @@
       <c r="G8" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="9">
         <v>1</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="11">
         <v>2450000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="8">
         <v>0.05</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="11">
         <f t="shared" si="0"/>
         <v>2327500</v>
       </c>
@@ -1172,7 +7525,7 @@
       <c r="A9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <v>46044</v>
       </c>
       <c r="C9" t="s">
@@ -1190,16 +7543,16 @@
       <c r="G9" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="9">
         <v>3</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="11">
         <v>185000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="8">
         <v>0.1</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="11">
         <f t="shared" si="0"/>
         <v>499500</v>
       </c>
@@ -1208,7 +7561,7 @@
       <c r="A10" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <v>46048</v>
       </c>
       <c r="C10" t="s">
@@ -1226,16 +7579,16 @@
       <c r="G10" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="9">
         <v>11</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="11">
         <v>310000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="8">
         <v>0.05</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="11">
         <f t="shared" si="0"/>
         <v>3239500</v>
       </c>
@@ -1244,7 +7597,7 @@
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <v>46049</v>
       </c>
       <c r="C11" t="s">
@@ -1262,16 +7615,16 @@
       <c r="G11" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="9">
         <v>2</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="11">
         <v>2450000</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="8">
         <v>0</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="11">
         <f t="shared" si="0"/>
         <v>4900000</v>
       </c>
@@ -1280,7 +7633,7 @@
       <c r="A12" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="7">
         <v>46053</v>
       </c>
       <c r="C12" t="s">
@@ -1298,16 +7651,16 @@
       <c r="G12" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="9">
         <v>1</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="11">
         <v>520000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="8">
         <v>0.1</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="11">
         <f t="shared" si="0"/>
         <v>468000</v>
       </c>
@@ -1316,7 +7669,7 @@
       <c r="A13" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <v>46055</v>
       </c>
       <c r="C13" t="s">
@@ -1334,16 +7687,16 @@
       <c r="G13" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="9">
         <v>1</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="11">
         <v>310000</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="8">
         <v>0.15</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="11">
         <f t="shared" si="0"/>
         <v>263500</v>
       </c>
@@ -1352,7 +7705,7 @@
       <c r="A14" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <v>46057</v>
       </c>
       <c r="C14" t="s">
@@ -1370,16 +7723,16 @@
       <c r="G14" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="9">
         <v>4</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="11">
         <v>520000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="8">
         <v>0</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="11">
         <f t="shared" si="0"/>
         <v>2080000</v>
       </c>
@@ -1388,7 +7741,7 @@
       <c r="A15" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
         <v>46059</v>
       </c>
       <c r="C15" t="s">
@@ -1406,16 +7759,16 @@
       <c r="G15" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="9">
         <v>1</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="11">
         <v>4200000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="8">
         <v>0</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="11">
         <f t="shared" si="0"/>
         <v>4200000</v>
       </c>
@@ -1424,7 +7777,7 @@
       <c r="A16" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="7">
         <v>46063</v>
       </c>
       <c r="C16" t="s">
@@ -1442,16 +7795,16 @@
       <c r="G16" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="9">
         <v>7</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="11">
         <v>310000</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="8">
         <v>0.15</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="11">
         <f t="shared" si="0"/>
         <v>1844500</v>
       </c>
@@ -1460,7 +7813,7 @@
       <c r="A17" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="7">
         <v>46065</v>
       </c>
       <c r="C17" t="s">
@@ -1478,16 +7831,16 @@
       <c r="G17" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="9">
         <v>2</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="11">
         <v>4200000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="8">
         <v>0.1</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="11">
         <f t="shared" si="0"/>
         <v>7560000</v>
       </c>
@@ -1496,7 +7849,7 @@
       <c r="A18" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="7">
         <v>46068</v>
       </c>
       <c r="C18" t="s">
@@ -1514,16 +7867,16 @@
       <c r="G18" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="9">
         <v>9</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="11">
         <v>94000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="8">
         <v>0.05</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="11">
         <f t="shared" si="0"/>
         <v>803700</v>
       </c>
@@ -1532,7 +7885,7 @@
       <c r="A19" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="7">
         <v>46070</v>
       </c>
       <c r="C19" t="s">
@@ -1550,16 +7903,16 @@
       <c r="G19" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="9">
         <v>8</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="11">
         <v>520000</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="8">
         <v>0.15</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="11">
         <f t="shared" si="0"/>
         <v>3536000</v>
       </c>
@@ -1568,7 +7921,7 @@
       <c r="A20" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="7">
         <v>46073</v>
       </c>
       <c r="C20" t="s">
@@ -1586,16 +7939,16 @@
       <c r="G20" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="9">
         <v>7</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="11">
         <v>68000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="8">
         <v>0</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="11">
         <f t="shared" si="0"/>
         <v>476000</v>
       </c>
@@ -1604,7 +7957,7 @@
       <c r="A21" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="7">
         <v>46075</v>
       </c>
       <c r="C21" t="s">
@@ -1622,16 +7975,16 @@
       <c r="G21" t="s">
         <v>16</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="9">
         <v>9</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="11">
         <v>185000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="8">
         <v>0</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="11">
         <f t="shared" si="0"/>
         <v>1665000</v>
       </c>
@@ -1640,7 +7993,7 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="7">
         <v>46077</v>
       </c>
       <c r="C22" t="s">
@@ -1658,16 +8011,16 @@
       <c r="G22" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="9">
         <v>2</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="11">
         <v>2450000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="8">
         <v>0.15</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="11">
         <f t="shared" si="0"/>
         <v>4165000</v>
       </c>
@@ -1676,7 +8029,7 @@
       <c r="A23" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="7">
         <v>46079</v>
       </c>
       <c r="C23" t="s">
@@ -1694,16 +8047,16 @@
       <c r="G23" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="9">
         <v>2</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="11">
         <v>68000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23" s="8">
         <v>0</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="11">
         <f t="shared" si="0"/>
         <v>136000</v>
       </c>
@@ -1712,7 +8065,7 @@
       <c r="A24" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="7">
         <v>46083</v>
       </c>
       <c r="C24" t="s">
@@ -1730,16 +8083,16 @@
       <c r="G24" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="9">
         <v>3</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="11">
         <v>310000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="8">
         <v>0.15</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="11">
         <f t="shared" si="0"/>
         <v>790500</v>
       </c>
@@ -1748,7 +8101,7 @@
       <c r="A25" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="7">
         <v>46085</v>
       </c>
       <c r="C25" t="s">
@@ -1766,16 +8119,16 @@
       <c r="G25" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="9">
         <v>2</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="11">
         <v>4200000</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J25" s="8">
         <v>0.05</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="11">
         <f t="shared" si="0"/>
         <v>7980000</v>
       </c>
@@ -1784,7 +8137,7 @@
       <c r="A26" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="7">
         <v>46088</v>
       </c>
       <c r="C26" t="s">
@@ -1802,16 +8155,16 @@
       <c r="G26" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="9">
         <v>2</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="11">
         <v>310000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="8">
         <v>0.05</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="11">
         <f t="shared" si="0"/>
         <v>589000</v>
       </c>
@@ -1820,7 +8173,7 @@
       <c r="A27" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="7">
         <v>46090</v>
       </c>
       <c r="C27" t="s">
@@ -1838,16 +8191,16 @@
       <c r="G27" t="s">
         <v>31</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="9">
         <v>3</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="11">
         <v>760000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="8">
         <v>0.1</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="11">
         <f t="shared" si="0"/>
         <v>2052000</v>
       </c>
@@ -1856,7 +8209,7 @@
       <c r="A28" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="7">
         <v>46093</v>
       </c>
       <c r="C28" t="s">
@@ -1874,16 +8227,16 @@
       <c r="G28" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="9">
         <v>6</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="11">
         <v>185000</v>
       </c>
-      <c r="J28" s="3">
+      <c r="J28" s="8">
         <v>0</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="11">
         <f t="shared" si="0"/>
         <v>1110000</v>
       </c>
@@ -1892,7 +8245,7 @@
       <c r="A29" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="7">
         <v>46094</v>
       </c>
       <c r="C29" t="s">
@@ -1910,16 +8263,16 @@
       <c r="G29" t="s">
         <v>22</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="9">
         <v>1</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="11">
         <v>520000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="8">
         <v>0</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="11">
         <f t="shared" si="0"/>
         <v>520000</v>
       </c>
@@ -1928,7 +8281,7 @@
       <c r="A30" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="7">
         <v>46098</v>
       </c>
       <c r="C30" t="s">
@@ -1946,16 +8299,16 @@
       <c r="G30" t="s">
         <v>16</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="9">
         <v>12</v>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="11">
         <v>760000</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="8">
         <v>0.05</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="11">
         <f t="shared" si="0"/>
         <v>8664000</v>
       </c>
@@ -1964,7 +8317,7 @@
       <c r="A31" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="7">
         <v>46100</v>
       </c>
       <c r="C31" t="s">
@@ -1982,16 +8335,16 @@
       <c r="G31" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="9">
         <v>8</v>
       </c>
-      <c r="I31" s="6">
+      <c r="I31" s="11">
         <v>68000</v>
       </c>
-      <c r="J31" s="3">
+      <c r="J31" s="8">
         <v>0</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="11">
         <f t="shared" si="0"/>
         <v>544000</v>
       </c>
@@ -2000,7 +8353,7 @@
       <c r="A32" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="7">
         <v>46102</v>
       </c>
       <c r="C32" t="s">
@@ -2018,16 +8371,16 @@
       <c r="G32" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="9">
         <v>8</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="11">
         <v>760000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="8">
         <v>0.15</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="11">
         <f t="shared" si="0"/>
         <v>5168000</v>
       </c>
@@ -2036,7 +8389,7 @@
       <c r="A33" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="7">
         <v>46105</v>
       </c>
       <c r="C33" t="s">
@@ -2054,16 +8407,16 @@
       <c r="G33" t="s">
         <v>16</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="9">
         <v>2</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="11">
         <v>4200000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J33" s="8">
         <v>0.15</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="11">
         <f t="shared" si="0"/>
         <v>7140000</v>
       </c>
@@ -2072,7 +8425,7 @@
       <c r="A34" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="7">
         <v>46108</v>
       </c>
       <c r="C34" t="s">
@@ -2090,16 +8443,16 @@
       <c r="G34" t="s">
         <v>22</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H34" s="9">
         <v>2</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="11">
         <v>185000</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="8">
         <v>0</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="11">
         <f t="shared" si="0"/>
         <v>370000</v>
       </c>
@@ -2108,7 +8461,7 @@
       <c r="A35" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="7">
         <v>46109</v>
       </c>
       <c r="C35" t="s">
@@ -2126,16 +8479,16 @@
       <c r="G35" t="s">
         <v>22</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H35" s="9">
         <v>11</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="11">
         <v>68000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="8">
         <v>0.05</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="11">
         <f t="shared" si="0"/>
         <v>710600</v>
       </c>
@@ -2144,7 +8497,7 @@
       <c r="A36" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="7">
         <v>46112</v>
       </c>
       <c r="C36" t="s">
@@ -2162,16 +8515,16 @@
       <c r="G36" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36" s="9">
         <v>6</v>
       </c>
-      <c r="I36" s="6">
+      <c r="I36" s="11">
         <v>310000</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="8">
         <v>0</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="11">
         <f t="shared" si="0"/>
         <v>1860000</v>
       </c>
@@ -2180,7 +8533,7 @@
       <c r="A37" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="7">
         <v>46115</v>
       </c>
       <c r="C37" t="s">
@@ -2198,16 +8551,16 @@
       <c r="G37" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H37" s="9">
         <v>2</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="11">
         <v>2450000</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="8">
         <v>0</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="11">
         <f t="shared" si="0"/>
         <v>4900000</v>
       </c>
@@ -2216,7 +8569,7 @@
       <c r="A38" t="s">
         <v>71</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="7">
         <v>46117</v>
       </c>
       <c r="C38" t="s">
@@ -2234,16 +8587,16 @@
       <c r="G38" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H38" s="9">
         <v>12</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="11">
         <v>520000</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J38" s="8">
         <v>0.05</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="11">
         <f t="shared" si="0"/>
         <v>5928000</v>
       </c>
@@ -2252,7 +8605,7 @@
       <c r="A39" t="s">
         <v>72</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="7">
         <v>46119</v>
       </c>
       <c r="C39" t="s">
@@ -2270,16 +8623,16 @@
       <c r="G39" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="4">
+      <c r="H39" s="9">
         <v>2</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="11">
         <v>4200000</v>
       </c>
-      <c r="J39" s="3">
+      <c r="J39" s="8">
         <v>0</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="11">
         <f t="shared" si="0"/>
         <v>8400000</v>
       </c>
@@ -2288,7 +8641,7 @@
       <c r="A40" t="s">
         <v>73</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="7">
         <v>46122</v>
       </c>
       <c r="C40" t="s">
@@ -2306,16 +8659,16 @@
       <c r="G40" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="4">
+      <c r="H40" s="9">
         <v>1</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="11">
         <v>2450000</v>
       </c>
-      <c r="J40" s="3">
+      <c r="J40" s="8">
         <v>0</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="11">
         <f t="shared" si="0"/>
         <v>2450000</v>
       </c>
@@ -2324,7 +8677,7 @@
       <c r="A41" t="s">
         <v>74</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="7">
         <v>46124</v>
       </c>
       <c r="C41" t="s">
@@ -2342,16 +8695,16 @@
       <c r="G41" t="s">
         <v>16</v>
       </c>
-      <c r="H41" s="4">
+      <c r="H41" s="9">
         <v>11</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="11">
         <v>68000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="8">
         <v>0.05</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="11">
         <f t="shared" si="0"/>
         <v>710600</v>
       </c>
@@ -2360,7 +8713,7 @@
       <c r="A42" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="7">
         <v>46127</v>
       </c>
       <c r="C42" t="s">
@@ -2378,16 +8731,16 @@
       <c r="G42" t="s">
         <v>31</v>
       </c>
-      <c r="H42" s="4">
+      <c r="H42" s="9">
         <v>5</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="11">
         <v>94000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="J42" s="8">
         <v>0</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="11">
         <f t="shared" si="0"/>
         <v>470000</v>
       </c>
@@ -2396,7 +8749,7 @@
       <c r="A43" t="s">
         <v>76</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="7">
         <v>46130</v>
       </c>
       <c r="C43" t="s">
@@ -2414,16 +8767,16 @@
       <c r="G43" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H43" s="9">
         <v>9</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="11">
         <v>760000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="8">
         <v>0.05</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="11">
         <f t="shared" si="0"/>
         <v>6498000</v>
       </c>
@@ -2432,7 +8785,7 @@
       <c r="A44" t="s">
         <v>77</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="7">
         <v>46132</v>
       </c>
       <c r="C44" t="s">
@@ -2450,16 +8803,16 @@
       <c r="G44" t="s">
         <v>16</v>
       </c>
-      <c r="H44" s="4">
+      <c r="H44" s="9">
         <v>1</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="11">
         <v>68000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="8">
         <v>0</v>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="11">
         <f t="shared" si="0"/>
         <v>68000</v>
       </c>
@@ -2468,7 +8821,7 @@
       <c r="A45" t="s">
         <v>78</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="7">
         <v>46134</v>
       </c>
       <c r="C45" t="s">
@@ -2486,16 +8839,16 @@
       <c r="G45" t="s">
         <v>16</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H45" s="9">
         <v>11</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="11">
         <v>185000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="8">
         <v>0.05</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="11">
         <f t="shared" si="0"/>
         <v>1933250</v>
       </c>
@@ -2504,7 +8857,7 @@
       <c r="A46" t="s">
         <v>79</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="7">
         <v>46138</v>
       </c>
       <c r="C46" t="s">
@@ -2522,16 +8875,16 @@
       <c r="G46" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="4">
+      <c r="H46" s="9">
         <v>6</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="11">
         <v>68000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="8">
         <v>0</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="11">
         <f t="shared" si="0"/>
         <v>408000</v>
       </c>
@@ -2540,7 +8893,7 @@
       <c r="A47" t="s">
         <v>80</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="7">
         <v>46140</v>
       </c>
       <c r="C47" t="s">
@@ -2558,16 +8911,16 @@
       <c r="G47" t="s">
         <v>31</v>
       </c>
-      <c r="H47" s="4">
+      <c r="H47" s="9">
         <v>10</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47" s="11">
         <v>310000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="8">
         <v>0</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="11">
         <f t="shared" si="0"/>
         <v>3100000</v>
       </c>
@@ -2576,7 +8929,7 @@
       <c r="A48" t="s">
         <v>81</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="7">
         <v>46142</v>
       </c>
       <c r="C48" t="s">
@@ -2594,16 +8947,16 @@
       <c r="G48" t="s">
         <v>22</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H48" s="9">
         <v>4</v>
       </c>
-      <c r="I48" s="6">
+      <c r="I48" s="11">
         <v>760000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="8">
         <v>0</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="11">
         <f t="shared" si="0"/>
         <v>3040000</v>
       </c>
@@ -2612,7 +8965,7 @@
       <c r="A49" t="s">
         <v>82</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="7">
         <v>46144</v>
       </c>
       <c r="C49" t="s">
@@ -2630,16 +8983,16 @@
       <c r="G49" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H49" s="9">
         <v>2</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I49" s="11">
         <v>4200000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="J49" s="8">
         <v>0</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="11">
         <f t="shared" si="0"/>
         <v>8400000</v>
       </c>
@@ -2648,7 +9001,7 @@
       <c r="A50" t="s">
         <v>83</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="7">
         <v>46147</v>
       </c>
       <c r="C50" t="s">
@@ -2666,16 +9019,16 @@
       <c r="G50" t="s">
         <v>31</v>
       </c>
-      <c r="H50" s="4">
+      <c r="H50" s="9">
         <v>3</v>
       </c>
-      <c r="I50" s="6">
+      <c r="I50" s="11">
         <v>760000</v>
       </c>
-      <c r="J50" s="3">
+      <c r="J50" s="8">
         <v>0</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="11">
         <f t="shared" si="0"/>
         <v>2280000</v>
       </c>
@@ -2684,7 +9037,7 @@
       <c r="A51" t="s">
         <v>84</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="7">
         <v>46149</v>
       </c>
       <c r="C51" t="s">
@@ -2702,16 +9055,16 @@
       <c r="G51" t="s">
         <v>16</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H51" s="9">
         <v>8</v>
       </c>
-      <c r="I51" s="6">
+      <c r="I51" s="11">
         <v>760000</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J51" s="8">
         <v>0</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="11">
         <f t="shared" si="0"/>
         <v>6080000</v>
       </c>
@@ -2720,7 +9073,7 @@
       <c r="A52" t="s">
         <v>85</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="7">
         <v>46152</v>
       </c>
       <c r="C52" t="s">
@@ -2738,16 +9091,16 @@
       <c r="G52" t="s">
         <v>31</v>
       </c>
-      <c r="H52" s="4">
+      <c r="H52" s="9">
         <v>1</v>
       </c>
-      <c r="I52" s="6">
+      <c r="I52" s="11">
         <v>520000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="8">
         <v>0.05</v>
       </c>
-      <c r="K52" s="6">
+      <c r="K52" s="11">
         <f t="shared" si="0"/>
         <v>494000</v>
       </c>
@@ -2756,7 +9109,7 @@
       <c r="A53" t="s">
         <v>86</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="7">
         <v>46154</v>
       </c>
       <c r="C53" t="s">
@@ -2774,16 +9127,16 @@
       <c r="G53" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="4">
+      <c r="H53" s="9">
         <v>10</v>
       </c>
-      <c r="I53" s="6">
+      <c r="I53" s="11">
         <v>760000</v>
       </c>
-      <c r="J53" s="3">
+      <c r="J53" s="8">
         <v>0</v>
       </c>
-      <c r="K53" s="6">
+      <c r="K53" s="11">
         <f t="shared" si="0"/>
         <v>7600000</v>
       </c>
@@ -2792,7 +9145,7 @@
       <c r="A54" t="s">
         <v>87</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="7">
         <v>46157</v>
       </c>
       <c r="C54" t="s">
@@ -2810,16 +9163,16 @@
       <c r="G54" t="s">
         <v>22</v>
       </c>
-      <c r="H54" s="4">
+      <c r="H54" s="9">
         <v>1</v>
       </c>
-      <c r="I54" s="6">
+      <c r="I54" s="11">
         <v>4200000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="J54" s="8">
         <v>0</v>
       </c>
-      <c r="K54" s="6">
+      <c r="K54" s="11">
         <f t="shared" si="0"/>
         <v>4200000</v>
       </c>
@@ -2828,7 +9181,7 @@
       <c r="A55" t="s">
         <v>88</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="7">
         <v>46160</v>
       </c>
       <c r="C55" t="s">
@@ -2846,16 +9199,16 @@
       <c r="G55" t="s">
         <v>16</v>
       </c>
-      <c r="H55" s="4">
+      <c r="H55" s="9">
         <v>1</v>
       </c>
-      <c r="I55" s="6">
+      <c r="I55" s="11">
         <v>2450000</v>
       </c>
-      <c r="J55" s="3">
+      <c r="J55" s="8">
         <v>0.1</v>
       </c>
-      <c r="K55" s="6">
+      <c r="K55" s="11">
         <f t="shared" si="0"/>
         <v>2205000</v>
       </c>
@@ -2864,7 +9217,7 @@
       <c r="A56" t="s">
         <v>89</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="7">
         <v>46163</v>
       </c>
       <c r="C56" t="s">
@@ -2882,16 +9235,16 @@
       <c r="G56" t="s">
         <v>16</v>
       </c>
-      <c r="H56" s="4">
+      <c r="H56" s="9">
         <v>2</v>
       </c>
-      <c r="I56" s="6">
+      <c r="I56" s="11">
         <v>4200000</v>
       </c>
-      <c r="J56" s="3">
+      <c r="J56" s="8">
         <v>0.05</v>
       </c>
-      <c r="K56" s="6">
+      <c r="K56" s="11">
         <f t="shared" si="0"/>
         <v>7980000</v>
       </c>
@@ -2900,7 +9253,7 @@
       <c r="A57" t="s">
         <v>90</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="7">
         <v>46165</v>
       </c>
       <c r="C57" t="s">
@@ -2918,16 +9271,16 @@
       <c r="G57" t="s">
         <v>22</v>
       </c>
-      <c r="H57" s="4">
+      <c r="H57" s="9">
         <v>10</v>
       </c>
-      <c r="I57" s="6">
+      <c r="I57" s="11">
         <v>185000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="8">
         <v>0.05</v>
       </c>
-      <c r="K57" s="6">
+      <c r="K57" s="11">
         <f t="shared" si="0"/>
         <v>1757500</v>
       </c>
@@ -2936,7 +9289,7 @@
       <c r="A58" t="s">
         <v>91</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="7">
         <v>46168</v>
       </c>
       <c r="C58" t="s">
@@ -2954,16 +9307,16 @@
       <c r="G58" t="s">
         <v>22</v>
       </c>
-      <c r="H58" s="4">
+      <c r="H58" s="9">
         <v>10</v>
       </c>
-      <c r="I58" s="6">
+      <c r="I58" s="11">
         <v>310000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="J58" s="8">
         <v>0.05</v>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="11">
         <f t="shared" si="0"/>
         <v>2945000</v>
       </c>
@@ -2972,7 +9325,7 @@
       <c r="A59" t="s">
         <v>92</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="7">
         <v>46170</v>
       </c>
       <c r="C59" t="s">
@@ -2990,16 +9343,16 @@
       <c r="G59" t="s">
         <v>31</v>
       </c>
-      <c r="H59" s="4">
+      <c r="H59" s="9">
         <v>2</v>
       </c>
-      <c r="I59" s="6">
+      <c r="I59" s="11">
         <v>4200000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="8">
         <v>0.05</v>
       </c>
-      <c r="K59" s="6">
+      <c r="K59" s="11">
         <f t="shared" si="0"/>
         <v>7980000</v>
       </c>
@@ -3008,7 +9361,7 @@
       <c r="A60" t="s">
         <v>93</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="7">
         <v>46172</v>
       </c>
       <c r="C60" t="s">
@@ -3026,16 +9379,16 @@
       <c r="G60" t="s">
         <v>16</v>
       </c>
-      <c r="H60" s="4">
+      <c r="H60" s="9">
         <v>7</v>
       </c>
-      <c r="I60" s="6">
+      <c r="I60" s="11">
         <v>310000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="J60" s="8">
         <v>0</v>
       </c>
-      <c r="K60" s="6">
+      <c r="K60" s="11">
         <f t="shared" si="0"/>
         <v>2170000</v>
       </c>
@@ -3044,7 +9397,7 @@
       <c r="A61" t="s">
         <v>94</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="7">
         <v>46174</v>
       </c>
       <c r="C61" t="s">
@@ -3062,16 +9415,16 @@
       <c r="G61" t="s">
         <v>31</v>
       </c>
-      <c r="H61" s="4">
+      <c r="H61" s="9">
         <v>11</v>
       </c>
-      <c r="I61" s="6">
+      <c r="I61" s="11">
         <v>94000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="J61" s="8">
         <v>0</v>
       </c>
-      <c r="K61" s="6">
+      <c r="K61" s="11">
         <f t="shared" si="0"/>
         <v>1034000</v>
       </c>
@@ -3080,7 +9433,7 @@
       <c r="A62" t="s">
         <v>95</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="7">
         <v>46178</v>
       </c>
       <c r="C62" t="s">
@@ -3098,16 +9451,16 @@
       <c r="G62" t="s">
         <v>22</v>
       </c>
-      <c r="H62" s="4">
+      <c r="H62" s="9">
         <v>2</v>
       </c>
-      <c r="I62" s="6">
+      <c r="I62" s="11">
         <v>2450000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="8">
         <v>0.05</v>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="11">
         <f t="shared" si="0"/>
         <v>4655000</v>
       </c>
@@ -3116,7 +9469,7 @@
       <c r="A63" t="s">
         <v>96</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="7">
         <v>46180</v>
       </c>
       <c r="C63" t="s">
@@ -3134,16 +9487,16 @@
       <c r="G63" t="s">
         <v>31</v>
       </c>
-      <c r="H63" s="4">
+      <c r="H63" s="9">
         <v>4</v>
       </c>
-      <c r="I63" s="6">
+      <c r="I63" s="11">
         <v>68000</v>
       </c>
-      <c r="J63" s="3">
+      <c r="J63" s="8">
         <v>0</v>
       </c>
-      <c r="K63" s="6">
+      <c r="K63" s="11">
         <f t="shared" si="0"/>
         <v>272000</v>
       </c>
@@ -3152,7 +9505,7 @@
       <c r="A64" t="s">
         <v>97</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="7">
         <v>46182</v>
       </c>
       <c r="C64" t="s">
@@ -3170,16 +9523,16 @@
       <c r="G64" t="s">
         <v>22</v>
       </c>
-      <c r="H64" s="4">
+      <c r="H64" s="9">
         <v>1</v>
       </c>
-      <c r="I64" s="6">
+      <c r="I64" s="11">
         <v>68000</v>
       </c>
-      <c r="J64" s="3">
+      <c r="J64" s="8">
         <v>0.1</v>
       </c>
-      <c r="K64" s="6">
+      <c r="K64" s="11">
         <f t="shared" si="0"/>
         <v>61200</v>
       </c>
@@ -3188,7 +9541,7 @@
       <c r="A65" t="s">
         <v>98</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="7">
         <v>46185</v>
       </c>
       <c r="C65" t="s">
@@ -3206,16 +9559,16 @@
       <c r="G65" t="s">
         <v>31</v>
       </c>
-      <c r="H65" s="4">
+      <c r="H65" s="9">
         <v>11</v>
       </c>
-      <c r="I65" s="6">
+      <c r="I65" s="11">
         <v>520000</v>
       </c>
-      <c r="J65" s="3">
+      <c r="J65" s="8">
         <v>0.15</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="11">
         <f t="shared" si="0"/>
         <v>4862000</v>
       </c>
@@ -3224,7 +9577,7 @@
       <c r="A66" t="s">
         <v>99</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="7">
         <v>46188</v>
       </c>
       <c r="C66" t="s">
@@ -3242,16 +9595,16 @@
       <c r="G66" t="s">
         <v>16</v>
       </c>
-      <c r="H66" s="4">
+      <c r="H66" s="9">
         <v>4</v>
       </c>
-      <c r="I66" s="6">
+      <c r="I66" s="11">
         <v>310000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="8">
         <v>0</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="11">
         <f t="shared" si="0"/>
         <v>1240000</v>
       </c>
@@ -3260,7 +9613,7 @@
       <c r="A67" t="s">
         <v>100</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="7">
         <v>46190</v>
       </c>
       <c r="C67" t="s">
@@ -3278,16 +9631,16 @@
       <c r="G67" t="s">
         <v>22</v>
       </c>
-      <c r="H67" s="4">
+      <c r="H67" s="9">
         <v>11</v>
       </c>
-      <c r="I67" s="6">
+      <c r="I67" s="11">
         <v>185000</v>
       </c>
-      <c r="J67" s="3">
+      <c r="J67" s="8">
         <v>0</v>
       </c>
-      <c r="K67" s="6">
+      <c r="K67" s="11">
         <f t="shared" ref="K67:K81" si="1">H67*I67*(1-J67)</f>
         <v>2035000</v>
       </c>
@@ -3296,7 +9649,7 @@
       <c r="A68" t="s">
         <v>101</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="7">
         <v>46192</v>
       </c>
       <c r="C68" t="s">
@@ -3314,16 +9667,16 @@
       <c r="G68" t="s">
         <v>31</v>
       </c>
-      <c r="H68" s="4">
+      <c r="H68" s="9">
         <v>11</v>
       </c>
-      <c r="I68" s="6">
+      <c r="I68" s="11">
         <v>760000</v>
       </c>
-      <c r="J68" s="3">
+      <c r="J68" s="8">
         <v>0.05</v>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="11">
         <f t="shared" si="1"/>
         <v>7942000</v>
       </c>
@@ -3332,7 +9685,7 @@
       <c r="A69" t="s">
         <v>102</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="7">
         <v>46195</v>
       </c>
       <c r="C69" t="s">
@@ -3350,16 +9703,16 @@
       <c r="G69" t="s">
         <v>22</v>
       </c>
-      <c r="H69" s="4">
+      <c r="H69" s="9">
         <v>2</v>
       </c>
-      <c r="I69" s="6">
+      <c r="I69" s="11">
         <v>2450000</v>
       </c>
-      <c r="J69" s="3">
+      <c r="J69" s="8">
         <v>0</v>
       </c>
-      <c r="K69" s="6">
+      <c r="K69" s="11">
         <f t="shared" si="1"/>
         <v>4900000</v>
       </c>
@@ -3368,7 +9721,7 @@
       <c r="A70" t="s">
         <v>103</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="7">
         <v>46197</v>
       </c>
       <c r="C70" t="s">
@@ -3386,16 +9739,16 @@
       <c r="G70" t="s">
         <v>22</v>
       </c>
-      <c r="H70" s="4">
+      <c r="H70" s="9">
         <v>8</v>
       </c>
-      <c r="I70" s="6">
+      <c r="I70" s="11">
         <v>94000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="J70" s="8">
         <v>0.05</v>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="11">
         <f t="shared" si="1"/>
         <v>714400</v>
       </c>
@@ -3404,7 +9757,7 @@
       <c r="A71" t="s">
         <v>104</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="7">
         <v>46200</v>
       </c>
       <c r="C71" t="s">
@@ -3422,16 +9775,16 @@
       <c r="G71" t="s">
         <v>22</v>
       </c>
-      <c r="H71" s="4">
+      <c r="H71" s="9">
         <v>7</v>
       </c>
-      <c r="I71" s="6">
+      <c r="I71" s="11">
         <v>520000</v>
       </c>
-      <c r="J71" s="3">
+      <c r="J71" s="8">
         <v>0.05</v>
       </c>
-      <c r="K71" s="6">
+      <c r="K71" s="11">
         <f t="shared" si="1"/>
         <v>3458000</v>
       </c>
@@ -3440,7 +9793,7 @@
       <c r="A72" t="s">
         <v>105</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="7">
         <v>46203</v>
       </c>
       <c r="C72" t="s">
@@ -3458,16 +9811,16 @@
       <c r="G72" t="s">
         <v>31</v>
       </c>
-      <c r="H72" s="4">
+      <c r="H72" s="9">
         <v>2</v>
       </c>
-      <c r="I72" s="6">
+      <c r="I72" s="11">
         <v>4200000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="8">
         <v>0.1</v>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="11">
         <f t="shared" si="1"/>
         <v>7560000</v>
       </c>
@@ -3476,7 +9829,7 @@
       <c r="A73" t="s">
         <v>106</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="7">
         <v>46204</v>
       </c>
       <c r="C73" t="s">
@@ -3494,16 +9847,16 @@
       <c r="G73" t="s">
         <v>16</v>
       </c>
-      <c r="H73" s="4">
+      <c r="H73" s="9">
         <v>1</v>
       </c>
-      <c r="I73" s="6">
+      <c r="I73" s="11">
         <v>68000</v>
       </c>
-      <c r="J73" s="3">
+      <c r="J73" s="8">
         <v>0.15</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="11">
         <f t="shared" si="1"/>
         <v>57800</v>
       </c>
@@ -3512,7 +9865,7 @@
       <c r="A74" t="s">
         <v>107</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="7">
         <v>46207</v>
       </c>
       <c r="C74" t="s">
@@ -3530,16 +9883,16 @@
       <c r="G74" t="s">
         <v>31</v>
       </c>
-      <c r="H74" s="4">
+      <c r="H74" s="9">
         <v>2</v>
       </c>
-      <c r="I74" s="6">
+      <c r="I74" s="11">
         <v>2450000</v>
       </c>
-      <c r="J74" s="3">
+      <c r="J74" s="8">
         <v>0</v>
       </c>
-      <c r="K74" s="6">
+      <c r="K74" s="11">
         <f t="shared" si="1"/>
         <v>4900000</v>
       </c>
@@ -3548,7 +9901,7 @@
       <c r="A75" t="s">
         <v>108</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="7">
         <v>46209</v>
       </c>
       <c r="C75" t="s">
@@ -3566,16 +9919,16 @@
       <c r="G75" t="s">
         <v>31</v>
       </c>
-      <c r="H75" s="4">
+      <c r="H75" s="9">
         <v>11</v>
       </c>
-      <c r="I75" s="6">
+      <c r="I75" s="11">
         <v>760000</v>
       </c>
-      <c r="J75" s="3">
+      <c r="J75" s="8">
         <v>0</v>
       </c>
-      <c r="K75" s="6">
+      <c r="K75" s="11">
         <f t="shared" si="1"/>
         <v>8360000</v>
       </c>
@@ -3584,7 +9937,7 @@
       <c r="A76" t="s">
         <v>109</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="7">
         <v>46212</v>
       </c>
       <c r="C76" t="s">
@@ -3602,16 +9955,16 @@
       <c r="G76" t="s">
         <v>22</v>
       </c>
-      <c r="H76" s="4">
+      <c r="H76" s="9">
         <v>3</v>
       </c>
-      <c r="I76" s="6">
+      <c r="I76" s="11">
         <v>310000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="J76" s="8">
         <v>0.05</v>
       </c>
-      <c r="K76" s="6">
+      <c r="K76" s="11">
         <f t="shared" si="1"/>
         <v>883500</v>
       </c>
@@ -3620,7 +9973,7 @@
       <c r="A77" t="s">
         <v>110</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="7">
         <v>46215</v>
       </c>
       <c r="C77" t="s">
@@ -3638,16 +9991,16 @@
       <c r="G77" t="s">
         <v>22</v>
       </c>
-      <c r="H77" s="4">
+      <c r="H77" s="9">
         <v>3</v>
       </c>
-      <c r="I77" s="6">
+      <c r="I77" s="11">
         <v>185000</v>
       </c>
-      <c r="J77" s="3">
+      <c r="J77" s="8">
         <v>0</v>
       </c>
-      <c r="K77" s="6">
+      <c r="K77" s="11">
         <f t="shared" si="1"/>
         <v>555000</v>
       </c>
@@ -3656,7 +10009,7 @@
       <c r="A78" t="s">
         <v>111</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="7">
         <v>46218</v>
       </c>
       <c r="C78" t="s">
@@ -3674,16 +10027,16 @@
       <c r="G78" t="s">
         <v>22</v>
       </c>
-      <c r="H78" s="4">
+      <c r="H78" s="9">
         <v>12</v>
       </c>
-      <c r="I78" s="6">
+      <c r="I78" s="11">
         <v>760000</v>
       </c>
-      <c r="J78" s="3">
+      <c r="J78" s="8">
         <v>0.1</v>
       </c>
-      <c r="K78" s="6">
+      <c r="K78" s="11">
         <f t="shared" si="1"/>
         <v>8208000</v>
       </c>
@@ -3692,7 +10045,7 @@
       <c r="A79" t="s">
         <v>112</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="7">
         <v>46220</v>
       </c>
       <c r="C79" t="s">
@@ -3710,16 +10063,16 @@
       <c r="G79" t="s">
         <v>31</v>
       </c>
-      <c r="H79" s="4">
+      <c r="H79" s="9">
         <v>2</v>
       </c>
-      <c r="I79" s="6">
+      <c r="I79" s="11">
         <v>520000</v>
       </c>
-      <c r="J79" s="3">
+      <c r="J79" s="8">
         <v>0</v>
       </c>
-      <c r="K79" s="6">
+      <c r="K79" s="11">
         <f t="shared" si="1"/>
         <v>1040000</v>
       </c>
@@ -3728,7 +10081,7 @@
       <c r="A80" t="s">
         <v>113</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="7">
         <v>46222</v>
       </c>
       <c r="C80" t="s">
@@ -3746,16 +10099,16 @@
       <c r="G80" t="s">
         <v>31</v>
       </c>
-      <c r="H80" s="4">
+      <c r="H80" s="9">
         <v>8</v>
       </c>
-      <c r="I80" s="6">
+      <c r="I80" s="11">
         <v>310000</v>
       </c>
-      <c r="J80" s="3">
+      <c r="J80" s="8">
         <v>0</v>
       </c>
-      <c r="K80" s="6">
+      <c r="K80" s="11">
         <f t="shared" si="1"/>
         <v>2480000</v>
       </c>
@@ -3764,7 +10117,7 @@
       <c r="A81" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="7">
         <v>46224</v>
       </c>
       <c r="C81" t="s">
@@ -3782,21 +10135,44 @@
       <c r="G81" t="s">
         <v>22</v>
       </c>
-      <c r="H81" s="4">
+      <c r="H81" s="9">
         <v>6</v>
       </c>
-      <c r="I81" s="6">
+      <c r="I81" s="11">
         <v>94000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="J81" s="8">
         <v>0.15</v>
       </c>
-      <c r="K81" s="6">
+      <c r="K81" s="11">
         <f t="shared" si="1"/>
         <v>479400</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{38BEF8D7-1F2D-4655-8B11-ABFFDE867FC5}">
+          <x14:colorSeries theme="3" tint="0.34998626667073579"/>
+          <x14:colorNegative theme="0" tint="-0.249977111117893"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="0" tint="-0.249977111117893"/>
+          <x14:colorFirst theme="0" tint="-0.249977111117893"/>
+          <x14:colorLast theme="0" tint="-0.249977111117893"/>
+          <x14:colorHigh theme="0" tint="-0.249977111117893"/>
+          <x14:colorLow theme="0" tint="-0.249977111117893"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Ventas!K2</xm:f>
+              <xm:sqref>L2</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
 </worksheet>
 </file>